--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EFC356-A670-984C-8A42-2FF99CB30B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FD146E-D17B-5F41-AC7A-8E89C5247E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -2560,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="8">
         <v>46107</v>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FD146E-D17B-5F41-AC7A-8E89C5247E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FBE8BF4-8285-4B7A-A546-7C2DC05C947D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -555,20 +555,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,1943 +901,1940 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="7"/>
-    <col min="2" max="2" width="13.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="7" customWidth="1"/>
-    <col min="6" max="8" width="8.83203125" style="7"/>
-    <col min="9" max="11" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="7"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="str">
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F2" s="7" t="str">
+      <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="4">
         <v>46082</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7" t="str">
+      <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F3" s="7" t="str">
+      <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G3" s="7">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="4">
         <v>46086</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="str">
+      <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I4" s="7">
-        <v>1</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
         <v>46086</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G5" s="7">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="4">
         <v>46087</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F6" s="7" t="str">
+      <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="4">
         <v>46087</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7" t="str">
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="4">
         <v>46088</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F8" s="7" t="str">
+      <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="4">
         <v>46088</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
         <v>0.52083333333333337</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="5">
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="str">
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F9" s="7" t="str">
+      <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="4">
         <v>46090</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="str">
+      <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10">
         <v>11</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="4">
         <v>46093</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="7" t="str">
+      <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F11" s="7" t="str">
+      <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11">
         <v>7</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="4">
         <v>46094</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="7">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="7" t="str">
+      <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F12" s="7" t="str">
+      <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="7">
-        <v>2</v>
-      </c>
-      <c r="J12" s="8">
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4">
         <v>46094</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="5">
         <v>0.75</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="7" t="str">
+      <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F13" s="7" t="str">
+      <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13">
         <v>12</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="4">
         <v>46095</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="5">
         <v>0.75</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F14" s="7" t="str">
+      <c r="F14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I14" s="7">
-        <v>2</v>
-      </c>
-      <c r="J14" s="8">
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
         <v>46099</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="5">
         <v>0.75</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="7">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="7" t="str">
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F15" s="7" t="str">
+      <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15">
         <v>7</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="4">
         <v>46100</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="7">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="7" t="str">
+      <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F16" s="7" t="str">
+      <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16">
         <v>12</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="4">
         <v>46101</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="7" t="str">
+      <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F17" s="7" t="str">
+      <c r="F17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="7">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8">
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
         <v>46101</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="7">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="7" t="str">
+      <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F18" s="7" t="str">
+      <c r="F18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="7">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8">
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
         <v>46102</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="7">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="7" t="str">
+      <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F19" s="7" t="str">
+      <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="7">
-        <v>2</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4">
         <v>46103</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="7">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" t="s">
         <v>134</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="7" t="str">
+      <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F20" s="7" t="str">
+      <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I20" s="7">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
         <v>46104</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="7">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="7" t="str">
+      <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F21" s="7" t="str">
+      <c r="F21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G21" s="7">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="7">
-        <v>2</v>
-      </c>
-      <c r="J21" s="8">
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21" s="4">
         <v>46109</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="5">
         <v>0.66666666666666663</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="7">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="7" t="str">
+      <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F22" s="7" t="str">
+      <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G22" s="7">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22">
         <v>12</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="4">
         <v>46102</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="5">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L22" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+      <c r="L22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="7" t="str">
+      <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F23" s="7" t="str">
+      <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G23" s="7">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23">
         <v>12</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="4">
         <v>46108</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="7" t="str">
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F24" s="7" t="str">
+      <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24">
         <v>7</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="4">
         <v>46110</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="5">
         <v>0.58333333333333337</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="5">
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="7">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="7" t="str">
+      <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F25" s="7" t="str">
+      <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I25" s="7">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8">
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
         <v>46095</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="5">
         <v>0.75</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F26" s="7" t="str">
+      <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I26" s="7">
-        <v>1</v>
-      </c>
-      <c r="J26" s="8">
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
         <v>46102</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="5">
         <v>0.75</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="7">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="7" t="str">
+      <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F27" s="7" t="str">
+      <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I27" s="7">
-        <v>1</v>
-      </c>
-      <c r="J27" s="8">
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
         <v>46109</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="5">
         <v>0.75</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="7" t="str">
+      <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F28" s="7" t="str">
+      <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I28" s="7">
-        <v>2</v>
-      </c>
-      <c r="J28" s="8">
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4">
         <v>46088</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="5">
         <v>0.5</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="7" t="str">
+      <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F29" s="7" t="str">
+      <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G29" s="7">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I29" s="7">
-        <v>2</v>
-      </c>
-      <c r="J29" s="8">
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4">
         <v>46102</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="5">
         <v>0.5</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="7" t="str">
+      <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F30" s="7" t="str">
+      <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I30" s="7">
-        <v>2</v>
-      </c>
-      <c r="J30" s="8">
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4">
         <v>46109</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="5">
         <v>0.5</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="7" t="str">
+      <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F31" s="7" t="str">
+      <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I31" s="7">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8">
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="4">
         <v>46085</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="7" t="str">
+      <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F32" s="7" t="str">
+      <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I32" s="7">
-        <v>1</v>
-      </c>
-      <c r="J32" s="8">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
         <v>46092</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="7">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="7" t="str">
+      <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F33" s="7" t="str">
+      <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G33" s="7">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I33" s="7">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8">
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4">
         <v>46099</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="7">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="7" t="str">
+      <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F34" s="7" t="str">
+      <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G34" s="7">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I34" s="7">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8">
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
         <v>46106</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="7">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="7" t="str">
+      <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F35" s="7" t="str">
+      <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G35" s="7">
-        <v>0</v>
-      </c>
-      <c r="H35" s="7">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I35" s="7">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8">
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="4">
         <v>46091</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="7">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="7" t="str">
+      <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F36" s="7" t="str">
+      <c r="F36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G36" s="7">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I36" s="7">
-        <v>2</v>
-      </c>
-      <c r="J36" s="8">
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36" s="4">
         <v>46098</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" t="s">
         <v>140</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" t="s">
         <v>6</v>
       </c>
-      <c r="D37" s="7" t="str">
+      <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F37" s="7" t="str">
+      <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G37" s="7">
-        <v>0</v>
-      </c>
-      <c r="H37" s="7">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I37" s="7">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8">
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4">
         <v>46097</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="7">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="7" t="str">
+      <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F38" s="7" t="str">
+      <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I38" s="7">
-        <v>2</v>
-      </c>
-      <c r="J38" s="8">
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
         <v>46103</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="5">
         <v>0.5</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="7">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="7" t="str">
+      <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F39" s="7" t="str">
+      <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G39" s="7">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I39" s="7">
-        <v>1</v>
-      </c>
-      <c r="J39" s="8">
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
         <v>46107</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="7">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="7" t="str">
+      <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F40" s="7" t="str">
+      <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I40" s="7">
-        <v>2</v>
-      </c>
-      <c r="J40" s="8">
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40" s="4">
         <v>46134</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="5">
         <v>0.625</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="5">
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="7">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" t="s">
         <v>142</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="7" t="str">
+      <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F41" s="7" t="str">
+      <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I41" s="7">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8">
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
         <v>46087</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="7">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" t="s">
         <v>143</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="7" t="str">
+      <c r="D42" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F42" s="7" t="str">
+      <c r="F42" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G42" s="7">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I42" s="7">
-        <v>2</v>
-      </c>
-      <c r="J42" s="8">
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" s="4">
         <v>46092</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="7">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="7" t="str">
+      <c r="D43" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F43" s="7" t="str">
+      <c r="F43" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G43" s="7">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I43" s="7">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8">
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
         <v>46112</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="5">
         <v>0.75</v>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J44" s="8"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J45" s="8"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J46" s="8"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J47" s="8"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J48" s="8"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-    </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J49" s="8"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-    </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J50" s="8"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-    </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J51" s="8"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-    </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J52" s="8"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-    </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J53" s="8"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-    </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J54" s="8"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J55" s="8"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-    </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J56" s="8"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-    </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J57" s="8"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-    </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J58" s="8"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-    </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J59" s="8"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-    </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J60" s="8"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-    </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J61" s="8"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-    </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J62" s="8"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J63" s="8"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J46" s="4"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J53" s="4"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2863,14 +2857,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -2881,7 +2875,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2892,7 +2886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2903,7 +2897,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2914,7 +2908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2925,7 +2919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2936,7 +2930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2947,7 +2941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2958,7 +2952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2969,7 +2963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2980,7 +2974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2991,7 +2985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3002,7 +2996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3013,7 +3007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3024,7 +3018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3035,7 +3029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3046,7 +3040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3057,7 +3051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3079,7 +3073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3090,7 +3084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3101,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3112,7 +3106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3123,7 +3117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3134,7 +3128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3145,7 +3139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3156,7 +3150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3167,7 +3161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3189,7 +3183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3200,7 +3194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3211,7 +3205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3222,7 +3216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3233,7 +3227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3244,7 +3238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3255,7 +3249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3266,7 +3260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3277,7 +3271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3288,7 +3282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3299,7 +3293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3310,7 +3304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3321,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3340,13 +3334,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="32" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -3444,7 +3438,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3542,12 +3536,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3561,7 +3555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3575,12 +3569,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3678,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3776,12 +3770,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3813,22 +3807,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3839,7 +3833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3847,12 +3841,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3860,12 +3854,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3915,17 +3909,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4023,7 +4017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4034,7 +4028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4132,7 +4126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4152,7 +4146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4250,12 +4244,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4263,7 +4257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4274,7 +4268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4288,17 +4282,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4347,7 +4341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4391,17 +4385,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4412,7 +4406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4420,7 +4414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4428,7 +4422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4451,7 +4445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4464,13 +4458,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4644,7 +4638,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4654,7 +4648,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4664,7 +4658,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4674,7 +4668,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4684,7 +4678,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4694,7 +4688,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4704,7 +4698,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4714,7 +4708,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4724,7 +4718,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4734,7 +4728,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4744,7 +4738,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4754,7 +4748,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4764,7 +4758,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4774,7 +4768,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4784,7 +4778,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4794,7 +4788,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4804,7 +4798,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4814,7 +4808,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4824,7 +4818,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4834,7 +4828,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4844,7 +4838,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4854,7 +4848,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4864,7 +4858,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4874,7 +4868,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4884,7 +4878,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4894,7 +4888,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4904,7 +4898,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4914,7 +4908,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4924,7 +4918,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4934,7 +4928,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4944,7 +4938,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4954,7 +4948,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4964,7 +4958,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4974,7 +4968,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4984,7 +4978,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4994,7 +4988,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -5004,7 +4998,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -5014,7 +5008,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -5024,7 +5018,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
@@ -5034,7 +5028,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -5044,7 +5038,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -5054,7 +5048,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -5072,12 +5066,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -5088,7 +5082,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -5099,7 +5093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -5110,7 +5104,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -5121,7 +5115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -5132,7 +5126,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -5143,7 +5137,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -5155,7 +5149,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -5166,7 +5160,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -5177,7 +5171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -5188,7 +5182,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -5199,7 +5193,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -5210,7 +5204,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5221,7 +5215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5232,7 +5226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5243,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5254,7 +5248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5265,7 +5259,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5276,7 +5270,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5287,7 +5281,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -5298,7 +5292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -5309,7 +5303,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -5320,7 +5314,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -5331,7 +5325,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -5342,7 +5336,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -5353,7 +5347,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -5364,7 +5358,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -5376,7 +5370,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -5388,7 +5382,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -5400,7 +5394,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -5411,7 +5405,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -5422,7 +5416,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -5433,7 +5427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -5444,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>87</v>
       </c>
@@ -5455,7 +5449,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -5466,7 +5460,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -5485,14 +5479,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -5503,7 +5497,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5514,7 +5508,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5525,7 +5519,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5536,7 +5530,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5547,7 +5541,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5558,7 +5552,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5569,7 +5563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5580,7 +5574,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5591,7 +5585,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5610,20 +5604,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5634,7 +5628,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -5642,7 +5636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -5650,7 +5644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>32</v>
       </c>
@@ -5658,7 +5652,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -5666,7 +5660,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -5677,7 +5671,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -5685,7 +5679,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>37</v>
       </c>
@@ -5693,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -5701,7 +5695,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -5709,7 +5703,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -5720,7 +5714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>42</v>
       </c>
@@ -5728,7 +5722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>43</v>
       </c>
@@ -5736,7 +5730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>44</v>
       </c>
@@ -5744,7 +5738,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>45</v>
       </c>
@@ -5752,7 +5746,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5763,7 +5757,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>48</v>
       </c>
@@ -5772,7 +5766,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>49</v>
       </c>
@@ -5781,7 +5775,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>50</v>
       </c>
@@ -5790,7 +5784,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>51</v>
       </c>
@@ -5799,7 +5793,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -5810,7 +5804,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>54</v>
       </c>
@@ -5819,7 +5813,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>55</v>
       </c>
@@ -5828,7 +5822,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>56</v>
       </c>
@@ -5837,7 +5831,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -5848,12 +5842,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -5864,7 +5858,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>62</v>
       </c>
@@ -5872,7 +5866,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>61</v>
       </c>
@@ -5880,7 +5874,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>65</v>
       </c>
@@ -5888,7 +5882,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>64</v>
       </c>
@@ -5896,7 +5890,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>63</v>
       </c>
@@ -5904,7 +5898,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>85</v>
       </c>
@@ -5923,17 +5917,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5956,7 +5950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5979,7 +5973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6002,7 +5996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6025,7 +6019,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6048,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -6071,7 +6065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6094,7 +6088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6117,7 +6111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6140,7 +6134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -6163,7 +6157,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6186,7 +6180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -6209,7 +6203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6232,7 +6226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6255,7 +6249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6278,7 +6272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FBE8BF4-8285-4B7A-A546-7C2DC05C947D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A04F662-3486-4D88-9AD0-820286FE6558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -2600,7 +2600,7 @@
         <v>2</v>
       </c>
       <c r="J40" s="4">
-        <v>46134</v>
+        <v>46103</v>
       </c>
       <c r="K40" s="5">
         <v>0.625</v>
@@ -3337,7 +3337,15 @@
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
@@ -5025,7 +5033,7 @@
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46134</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A04F662-3486-4D88-9AD0-820286FE6558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7AB909-439A-9D42-8537-1E6AA04F772E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -555,17 +555,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,1940 +904,1943 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="7"/>
+    <col min="2" max="2" width="13.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" style="7" customWidth="1"/>
+    <col min="6" max="8" width="8.83203125" style="7"/>
+    <col min="9" max="11" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="str">
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="7">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F2" s="7" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="7">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="7">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="7">
         <v>10</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="8">
         <v>46082</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="9">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="9">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="7" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="7">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3" s="7" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="G3" s="7">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="7">
         <v>12</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="8">
         <v>46086</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="9">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="7" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="7">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F4" t="str">
+      <c r="F4" s="7" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="7">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="7">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="I4" s="7">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8">
         <v>46086</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="7" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="7">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F5" s="7" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
+      <c r="G5" s="7">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="7">
         <v>3</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="8">
         <v>46087</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="9">
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="7" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="7">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F6" s="7" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="7">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="7">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="7">
         <v>11</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="8">
         <v>46087</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="9">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="str">
+      <c r="C7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F7" s="7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="7">
         <v>7</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="8">
         <v>46088</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="9">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D8" s="7" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="7">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F8" s="7" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="7">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="7">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="7">
         <v>10</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="8">
         <v>46088</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="9">
         <v>0.52083333333333337</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="9">
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="str">
+      <c r="C9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="7">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F9" t="str">
+      <c r="F9" s="7" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="7">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="7">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="8">
         <v>46090</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="7" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="7">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F10" s="7" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="7">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="7">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="7">
         <v>11</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="8">
         <v>46093</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="9">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="7" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="7">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F11" s="7" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="7">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="7">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="7">
         <v>7</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="8">
         <v>46094</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="9">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="9">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="7" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="7">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F12" s="7" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="7">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+      <c r="J12" s="8">
         <v>46094</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="9">
         <v>0.75</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="7" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="7">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F13" s="7" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="7">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="7">
         <v>12</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="8">
         <v>46095</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="9">
         <v>0.75</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D14" s="7" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="7">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F14" s="7" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4">
+      <c r="I14" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8">
         <v>46099</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="9">
         <v>0.75</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="str">
+      <c r="C15" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="7">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F15" t="str">
+      <c r="F15" s="7" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="7">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="7">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="7">
         <v>7</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="8">
         <v>46100</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D16" t="str">
+      <c r="D16" s="7" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="7">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F16" s="7" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="7">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="7">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="7">
         <v>12</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="8">
         <v>46101</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="9">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D17" t="str">
+      <c r="D17" s="7" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="7">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F17" s="7" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" s="4">
+      <c r="I17" s="7">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8">
         <v>46101</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D18" t="str">
+      <c r="D18" s="7" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="7">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F18" s="7" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4">
+      <c r="I18" s="7">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
         <v>46102</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="9">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D19" s="7" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="7">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F19" s="7" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="J19" s="4">
+      <c r="I19" s="7">
+        <v>2</v>
+      </c>
+      <c r="J19" s="8">
         <v>46103</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="9">
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D20" s="7" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="7">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F20" s="7" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4">
+      <c r="I20" s="7">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
         <v>46104</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="9">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="9">
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D21" s="7" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="7">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F21" t="str">
+      <c r="F21" s="7" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
+      <c r="G21" s="7">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-      <c r="J21" s="4">
+      <c r="I21" s="7">
+        <v>2</v>
+      </c>
+      <c r="J21" s="8">
         <v>46109</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D22" s="7" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="7">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F22" t="str">
+      <c r="F22" s="7" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
+      <c r="G22" s="7">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="7">
         <v>12</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="8">
         <v>46102</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="9">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D23" s="7" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="7">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F23" t="str">
+      <c r="F23" s="7" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="7">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="7">
         <v>12</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="8">
         <v>46108</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="str">
+      <c r="C24" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="7">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F24" s="7" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="7">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="7">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="7">
         <v>7</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="8">
         <v>46110</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="9">
         <v>0.58333333333333337</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="9">
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D25" s="7" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="7">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F25" t="str">
+      <c r="F25" s="7" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="7">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="7">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25" s="4">
+      <c r="I25" s="7">
+        <v>1</v>
+      </c>
+      <c r="J25" s="8">
         <v>46095</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="9">
         <v>0.75</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D26" t="str">
+      <c r="D26" s="7" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="7">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F26" s="7" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="7">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="7">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26" s="4">
+      <c r="I26" s="7">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8">
         <v>46102</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="9">
         <v>0.75</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D27" s="7" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="7">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F27" s="7" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="7">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="7">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27" s="4">
+      <c r="I27" s="7">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8">
         <v>46109</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="9">
         <v>0.75</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D28" s="7" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="7">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F28" s="7" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="7">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="7">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4">
+      <c r="I28" s="7">
+        <v>2</v>
+      </c>
+      <c r="J28" s="8">
         <v>46088</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="9">
         <v>0.5</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="9">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D29" s="7" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="7">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F29" s="7" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
+      <c r="G29" s="7">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I29">
-        <v>2</v>
-      </c>
-      <c r="J29" s="4">
+      <c r="I29" s="7">
+        <v>2</v>
+      </c>
+      <c r="J29" s="8">
         <v>46102</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="9">
         <v>0.5</v>
       </c>
-      <c r="L29" s="5">
+      <c r="L29" s="9">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D30" t="str">
+      <c r="D30" s="7" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="7">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F30" s="7" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="7">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="7">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I30">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4">
+      <c r="I30" s="7">
+        <v>2</v>
+      </c>
+      <c r="J30" s="8">
         <v>46109</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="9">
         <v>0.5</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30" s="9">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D31" s="7" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="7">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F31" t="str">
+      <c r="F31" s="7" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="7">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="7">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31" s="4">
+      <c r="I31" s="7">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8">
         <v>46085</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D32" s="7" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="7">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F32" t="str">
+      <c r="F32" s="7" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="7">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="7">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" s="4">
+      <c r="I32" s="7">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8">
         <v>46092</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L32" s="5">
+      <c r="L32" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D33" s="7" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="7">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F33" t="str">
+      <c r="F33" s="7" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33" s="4">
+      <c r="I33" s="7">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8">
         <v>46099</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L33" s="5">
+      <c r="L33" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="7">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D34" s="7" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="7">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>90</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F34" s="7" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34" s="4">
+      <c r="I34" s="7">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8">
         <v>46106</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L34" s="5">
+      <c r="L34" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D35" t="str">
+      <c r="D35" s="7" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="7">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F35" s="7" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
+      <c r="G35" s="7">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35" s="4">
+      <c r="I35" s="7">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8">
         <v>46091</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L35" s="5">
+      <c r="L35" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D36" s="7" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="7">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F36" s="7" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="G36" s="7">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I36">
-        <v>2</v>
-      </c>
-      <c r="J36" s="4">
+      <c r="I36" s="7">
+        <v>2</v>
+      </c>
+      <c r="J36" s="8">
         <v>46098</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D37" s="7" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="7">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F37" s="7" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
+      <c r="G37" s="7">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-      <c r="J37" s="4">
+      <c r="I37" s="7">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8">
         <v>46097</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K37" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L37" s="5">
+      <c r="L37" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="7">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D38" s="7" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="7">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F38" s="7" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="7">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="7">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I38">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4">
+      <c r="I38" s="7">
+        <v>2</v>
+      </c>
+      <c r="J38" s="8">
         <v>46103</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38" s="9">
         <v>0.5</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38" s="9">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="7">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D39" s="7" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="7">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F39" s="7" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
+      <c r="G39" s="7">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" s="4">
+      <c r="I39" s="7">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8">
         <v>46107</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K39" s="9">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39" s="9">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="7">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D40" s="7" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="7">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F40" s="7" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="7">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="7">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I40">
-        <v>2</v>
-      </c>
-      <c r="J40" s="4">
-        <v>46103</v>
-      </c>
-      <c r="K40" s="5">
+      <c r="I40" s="7">
+        <v>2</v>
+      </c>
+      <c r="J40" s="8">
+        <v>46096</v>
+      </c>
+      <c r="K40" s="9">
         <v>0.625</v>
       </c>
-      <c r="L40" s="5">
+      <c r="L40" s="9">
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="7">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D41" s="7" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="7">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F41" s="7" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="7">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="7">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" s="4">
+      <c r="I41" s="7">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8">
         <v>46087</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K41" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L41" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="7">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D42" s="7" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="7">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F42" s="7" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
+      <c r="G42" s="7">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I42">
-        <v>2</v>
-      </c>
-      <c r="J42" s="4">
+      <c r="I42" s="7">
+        <v>2</v>
+      </c>
+      <c r="J42" s="8">
         <v>46092</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="9">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="7">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D43" s="7" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="7">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F43" t="str">
+      <c r="F43" s="7" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
+      <c r="G43" s="7">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" s="4">
+      <c r="I43" s="7">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8">
         <v>46112</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43" s="9">
         <v>0.75</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="9">
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J44" s="4"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J45" s="4"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J46" s="4"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J47" s="4"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="J48" s="4"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J49" s="4"/>
-      <c r="K49" s="5"/>
-      <c r="L49" s="5"/>
-    </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J50" s="4"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J51" s="4"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-    </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J52" s="4"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="5"/>
-    </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J53" s="4"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-    </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J54" s="4"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-    </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J55" s="4"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-    </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J56" s="4"/>
-      <c r="K56" s="5"/>
-      <c r="L56" s="5"/>
-    </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J57" s="4"/>
-      <c r="K57" s="5"/>
-      <c r="L57" s="5"/>
-    </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J58" s="4"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="5"/>
-    </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J59" s="4"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-    </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J60" s="4"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-    </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J61" s="4"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-    </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J62" s="4"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J63" s="4"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J44" s="8"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J45" s="8"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J46" s="8"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J47" s="8"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J48" s="8"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+    </row>
+    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J49" s="8"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J50" s="8"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J51" s="8"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J52" s="8"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+    </row>
+    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J53" s="8"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J54" s="8"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J55" s="8"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J56" s="8"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J57" s="8"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J58" s="8"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+    </row>
+    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J59" s="8"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+    </row>
+    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J60" s="8"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J61" s="8"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+    </row>
+    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J62" s="8"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J63" s="8"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2857,14 +2863,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -2875,7 +2881,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2886,7 +2892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2897,7 +2903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2908,7 +2914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2930,7 +2936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2941,7 +2947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2952,7 +2958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2963,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2974,7 +2980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2985,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2996,7 +3002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3007,7 +3013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3018,7 +3024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3040,7 +3046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3051,7 +3057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3073,7 +3079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3084,7 +3090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3095,7 +3101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3106,7 +3112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3117,7 +3123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3128,7 +3134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3139,7 +3145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3150,7 +3156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3161,7 +3167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3194,7 +3200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3205,7 +3211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3216,7 +3222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3227,7 +3233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3238,7 +3244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3260,7 +3266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3271,7 +3277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3282,7 +3288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3293,7 +3299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3304,7 +3310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3315,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3334,21 +3340,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -3446,7 +3444,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3544,12 +3542,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3563,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3577,12 +3575,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3680,7 +3678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3778,12 +3776,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3815,22 +3813,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3841,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3849,12 +3847,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3862,12 +3860,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3917,17 +3915,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4025,7 +4023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4036,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4134,7 +4132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4154,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4252,12 +4250,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4265,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4276,7 +4274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4290,17 +4288,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4335,7 +4333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4349,7 +4347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4393,17 +4391,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4414,7 +4412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4422,7 +4420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4430,7 +4428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4453,7 +4451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4466,13 +4464,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4646,7 +4644,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4656,7 +4654,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4666,7 +4664,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4676,7 +4674,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4686,7 +4684,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4696,7 +4694,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4706,7 +4704,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4716,7 +4714,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4726,7 +4724,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4736,7 +4734,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4746,7 +4744,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4756,7 +4754,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4766,7 +4764,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4776,7 +4774,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4786,7 +4784,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4796,7 +4794,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4806,7 +4804,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4816,7 +4814,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4826,7 +4824,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4836,7 +4834,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4846,7 +4844,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4856,7 +4854,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4866,7 +4864,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4876,7 +4874,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4886,7 +4884,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4896,7 +4894,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4906,7 +4904,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4916,7 +4914,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4926,7 +4924,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4936,7 +4934,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4946,7 +4944,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4956,7 +4954,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4966,7 +4964,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4976,7 +4974,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4986,7 +4984,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4996,7 +4994,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -5006,7 +5004,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -5016,7 +5014,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -5026,17 +5024,17 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -5046,7 +5044,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -5056,7 +5054,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -5074,12 +5072,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -5090,7 +5088,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -5101,7 +5099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -5112,7 +5110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -5123,7 +5121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -5134,7 +5132,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -5145,7 +5143,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -5157,7 +5155,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -5168,7 +5166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>78</v>
       </c>
@@ -5179,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -5190,7 +5188,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -5201,7 +5199,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -5212,7 +5210,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5223,7 +5221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5234,7 +5232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5245,7 +5243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5256,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5267,7 +5265,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5278,7 +5276,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5289,7 +5287,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -5300,7 +5298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -5311,7 +5309,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>79</v>
       </c>
@@ -5322,7 +5320,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -5333,7 +5331,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -5344,7 +5342,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -5355,7 +5353,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -5366,7 +5364,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -5378,7 +5376,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -5390,7 +5388,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>80</v>
       </c>
@@ -5402,7 +5400,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>81</v>
       </c>
@@ -5413,7 +5411,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>86</v>
       </c>
@@ -5424,7 +5422,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -5435,7 +5433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -5446,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>87</v>
       </c>
@@ -5457,7 +5455,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -5468,7 +5466,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -5487,14 +5485,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -5505,7 +5503,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5516,7 +5514,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5527,7 +5525,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5538,7 +5536,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5549,7 +5547,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5560,7 +5558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5571,7 +5569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5582,7 +5580,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5593,7 +5591,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5612,20 +5610,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
   <dimension ref="A1:C41"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -5636,7 +5634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -5644,7 +5642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -5652,7 +5650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>32</v>
       </c>
@@ -5660,7 +5658,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -5668,7 +5666,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -5679,7 +5677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -5687,7 +5685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>37</v>
       </c>
@@ -5695,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>38</v>
       </c>
@@ -5703,7 +5701,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -5711,7 +5709,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -5722,7 +5720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>42</v>
       </c>
@@ -5730,7 +5728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>43</v>
       </c>
@@ -5738,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>44</v>
       </c>
@@ -5746,7 +5744,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>45</v>
       </c>
@@ -5754,7 +5752,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -5765,7 +5763,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>48</v>
       </c>
@@ -5774,7 +5772,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>49</v>
       </c>
@@ -5783,7 +5781,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>50</v>
       </c>
@@ -5792,7 +5790,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>51</v>
       </c>
@@ -5801,7 +5799,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -5812,7 +5810,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>54</v>
       </c>
@@ -5821,7 +5819,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>55</v>
       </c>
@@ -5830,7 +5828,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>56</v>
       </c>
@@ -5839,7 +5837,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -5850,12 +5848,12 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -5866,7 +5864,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>62</v>
       </c>
@@ -5874,7 +5872,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>61</v>
       </c>
@@ -5882,7 +5880,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>65</v>
       </c>
@@ -5890,7 +5888,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>64</v>
       </c>
@@ -5898,7 +5896,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>63</v>
       </c>
@@ -5906,7 +5904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>85</v>
       </c>
@@ -5925,17 +5923,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5958,7 +5956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5981,7 +5979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -6004,7 +6002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -6027,7 +6025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6050,7 +6048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -6073,7 +6071,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6096,7 +6094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6119,7 +6117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6142,7 +6140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -6165,7 +6163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6188,7 +6186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -6211,7 +6209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6234,7 +6232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6257,7 +6255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6280,7 +6278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7AB909-439A-9D42-8537-1E6AA04F772E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1A23D-5BC4-4640-B993-4F03B7D2B889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
@@ -1122,7 +1122,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L5" s="9">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1720,7 +1720,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L19" s="9">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -1762,7 +1762,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L20" s="9">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1A23D-5BC4-4640-B993-4F03B7D2B889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D62F44-E08D-4066-B401-B3CA353F3FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -126,123 +125,9 @@
     <t>EventRanking</t>
   </si>
   <si>
-    <t>Mínus</t>
-  </si>
-  <si>
-    <t>Helgi, kominn með aðra helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 4 helgar</t>
-  </si>
-  <si>
-    <t>Helgi, var með helgi síðast</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 5 helgar</t>
-  </si>
-  <si>
-    <t>Salur</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Vika</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Hvað hún er löng</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Langar vaktir</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
-  </si>
-  <si>
-    <t>Með hverjum?</t>
-  </si>
-  <si>
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 2 en þú ert 1</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert</t>
-  </si>
-  <si>
     <t>K&amp;B</t>
   </si>
   <si>
@@ -295,12 +180,6 @@
   </si>
   <si>
     <t>EmpSkillset</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 en þú ert ekki</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
   <si>
     <t>Req_this_shift</t>
@@ -555,20 +434,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,1943 +777,1940 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="7"/>
-    <col min="2" max="2" width="13.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" style="7" customWidth="1"/>
-    <col min="6" max="8" width="8.83203125" style="7"/>
-    <col min="9" max="11" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="7"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="str">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F2" s="7" t="str">
+      <c r="F2" t="str">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2">
         <f>_xlfn.XLOOKUP(C2,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="4">
         <v>46082</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7" t="str">
+      <c r="D3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F3" s="7" t="str">
+      <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G3" s="7">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3">
         <v>12</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="4">
         <v>46086</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="str">
+      <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I4" s="7">
-        <v>1</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
         <v>46086</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F5" s="7" t="str">
+      <c r="F5" t="str">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G5" s="7">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="4">
         <v>46087</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L5" s="9">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+      <c r="L5" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F6" s="7" t="str">
+      <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6">
         <v>11</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="4">
         <v>46087</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="7" t="str">
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F7" s="7" t="str">
+      <c r="F7" t="str">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7">
         <f>_xlfn.XLOOKUP(C7,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="4">
         <v>46088</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
-      </c>
-      <c r="F8" s="7" t="str">
+        <v>80</v>
+      </c>
+      <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>Fatahengi</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="4">
         <v>46088</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
         <v>0.52083333333333337</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="5">
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="str">
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F9" s="7" t="str">
+      <c r="F9" t="str">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9">
         <f>_xlfn.XLOOKUP(C9,EventTypes!A:A,EventTypes!G:G,"")</f>
         <v>11</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="4">
         <v>46090</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="str">
+      <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10">
         <v>11</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="4">
         <v>46093</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="7" t="str">
+      <c r="D11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F11" s="7" t="str">
+      <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>3</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11">
         <v>7</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="4">
         <v>46094</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="7">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="7" t="str">
+      <c r="D12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F12" s="7" t="str">
+      <c r="F12" t="str">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="7">
-        <v>2</v>
-      </c>
-      <c r="J12" s="8">
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4">
         <v>46094</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="5">
         <v>0.75</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="7" t="str">
+      <c r="D13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F13" s="7" t="str">
+      <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13">
         <v>12</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="4">
         <v>46095</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="5">
         <v>0.75</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F14" s="7" t="str">
+      <c r="F14" t="str">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
         <f>_xlfn.XLOOKUP(C14,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I14" s="7">
-        <v>2</v>
-      </c>
-      <c r="J14" s="8">
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
         <v>46099</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="5">
         <v>0.75</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="7">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="7" t="str">
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F15" s="7" t="str">
+      <c r="F15" t="str">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15">
         <f>_xlfn.XLOOKUP(C15,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15">
         <v>7</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="4">
         <v>46100</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="7">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="7" t="str">
+      <c r="D16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F16" s="7" t="str">
+      <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16">
         <v>12</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="4">
         <v>46101</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="5">
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="7" t="str">
+      <c r="D17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F17" s="7" t="str">
+      <c r="F17" t="str">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="7">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8">
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
         <v>46101</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="7">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="7" t="str">
+      <c r="D18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F18" s="7" t="str">
+      <c r="F18" t="str">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="7">
-        <v>1</v>
-      </c>
-      <c r="J18" s="8">
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
         <v>46102</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="5">
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="7">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="7" t="str">
+      <c r="D19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F19" s="7" t="str">
+      <c r="F19" t="str">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G19" s="7">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="7">
-        <v>2</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4">
         <v>46103</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L19" s="9">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="7">
+      <c r="L19" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="7" t="str">
+      <c r="D20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F20" s="7" t="str">
+      <c r="F20" t="str">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I20" s="7">
-        <v>1</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
         <v>46104</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="5">
         <v>0.77083333333333337</v>
       </c>
-      <c r="L20" s="9">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="7">
+      <c r="L20" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="7" t="str">
+      <c r="D21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F21" s="7" t="str">
+      <c r="F21" t="str">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G21" s="7">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="7">
-        <v>2</v>
-      </c>
-      <c r="J21" s="8">
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21" s="4">
         <v>46109</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="5">
         <v>0.66666666666666663</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="7">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="7" t="str">
+      <c r="D22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F22" s="7" t="str">
+      <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G22" s="7">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22">
         <v>12</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="4">
         <v>46102</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="5">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L22" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+      <c r="L22" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="7" t="str">
+      <c r="D23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Party</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>50</v>
       </c>
-      <c r="F23" s="7" t="str">
+      <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G23" s="7">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>6</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23">
         <v>12</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="4">
         <v>46108</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="7" t="str">
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>70</v>
       </c>
-      <c r="F24" s="7" t="str">
+      <c r="F24" t="str">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>EB</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>1</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24">
         <f>_xlfn.XLOOKUP(C24,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>4</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24">
         <v>7</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="4">
         <v>46110</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="5">
         <v>0.58333333333333337</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="5">
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="7">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="7" t="str">
+      <c r="D25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F25" s="7" t="str">
+      <c r="F25" t="str">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25">
         <f>_xlfn.XLOOKUP(C25,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I25" s="7">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8">
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
         <v>46095</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="5">
         <v>0.75</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="7" t="str">
+      <c r="D26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F26" s="7" t="str">
+      <c r="F26" t="str">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26">
         <f>_xlfn.XLOOKUP(C26,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I26" s="7">
-        <v>1</v>
-      </c>
-      <c r="J26" s="8">
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
         <v>46102</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="5">
         <v>0.75</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="7">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="7" t="str">
+      <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>100</v>
       </c>
-      <c r="F27" s="7" t="str">
+      <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I27" s="7">
-        <v>1</v>
-      </c>
-      <c r="J27" s="8">
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
         <v>46109</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="5">
         <v>0.75</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="7" t="s">
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="7" t="str">
+      <c r="D28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F28" s="7" t="str">
+      <c r="F28" t="str">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28">
         <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I28" s="7">
-        <v>2</v>
-      </c>
-      <c r="J28" s="8">
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28" s="4">
         <v>46088</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="5">
         <v>0.5</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="7" t="str">
+      <c r="D29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F29" s="7" t="str">
+      <c r="F29" t="str">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G29" s="7">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
         <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I29" s="7">
-        <v>2</v>
-      </c>
-      <c r="J29" s="8">
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4">
         <v>46102</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="5">
         <v>0.5</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="7" t="str">
+      <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F30" s="7" t="str">
+      <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I30" s="7">
-        <v>2</v>
-      </c>
-      <c r="J30" s="8">
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4">
         <v>46109</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="5">
         <v>0.5</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="7" t="str">
+      <c r="D31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F31" s="7" t="str">
+        <v>80</v>
+      </c>
+      <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I31" s="7">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8">
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="4">
         <v>46085</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="7" t="str">
+      <c r="D32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F32" s="7" t="str">
+        <v>80</v>
+      </c>
+      <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I32" s="7">
-        <v>1</v>
-      </c>
-      <c r="J32" s="8">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4">
         <v>46092</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="7">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="7" t="str">
+      <c r="D33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F33" s="7" t="str">
+        <v>80</v>
+      </c>
+      <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G33" s="7">
-        <v>0</v>
-      </c>
-      <c r="H33" s="7">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I33" s="7">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8">
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" s="4">
         <v>46099</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="7">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="7" t="str">
+      <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
-      </c>
-      <c r="F34" s="7" t="str">
+        <v>80</v>
+      </c>
+      <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
-      <c r="G34" s="7">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I34" s="7">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8">
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34" s="4">
         <v>46106</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="7">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C35" s="7" t="s">
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="7" t="str">
+      <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F35" s="7" t="str">
+      <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G35" s="7">
-        <v>0</v>
-      </c>
-      <c r="H35" s="7">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I35" s="7">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8">
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="4">
         <v>46091</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="7">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="7" t="s">
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="7" t="str">
+      <c r="D36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F36" s="7" t="str">
+      <c r="F36" t="str">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G36" s="7">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I36" s="7">
-        <v>2</v>
-      </c>
-      <c r="J36" s="8">
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36" s="4">
         <v>46098</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C37" s="7" t="s">
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
         <v>6</v>
       </c>
-      <c r="D37" s="7" t="str">
+      <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F37" s="7" t="str">
+      <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G37" s="7">
-        <v>0</v>
-      </c>
-      <c r="H37" s="7">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I37" s="7">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8">
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" s="4">
         <v>46097</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="7">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="7" t="str">
+      <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Barna</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F38" s="7" t="str">
+      <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I38" s="7">
-        <v>2</v>
-      </c>
-      <c r="J38" s="8">
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
         <v>46103</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="5">
         <v>0.5</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="5">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="7">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="7" t="s">
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="7" t="str">
+      <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F39" s="7" t="str">
+      <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>SB</v>
       </c>
-      <c r="G39" s="7">
-        <v>0</v>
-      </c>
-      <c r="H39" s="7">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I39" s="7">
-        <v>1</v>
-      </c>
-      <c r="J39" s="8">
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
         <v>46107</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="5">
         <v>0.70833333333333337</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="5">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="7">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="7" t="str">
+      <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Solo</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F40" s="7" t="str">
+        <v>90</v>
+      </c>
+      <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I40" s="7">
-        <v>2</v>
-      </c>
-      <c r="J40" s="8">
-        <v>46096</v>
-      </c>
-      <c r="K40" s="9">
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40" s="4">
+        <v>46103</v>
+      </c>
+      <c r="K40" s="5">
         <v>0.625</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="5">
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="7">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" s="7" t="s">
+      <c r="B41" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="7" t="str">
+      <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>40</v>
       </c>
-      <c r="F41" s="7" t="str">
+      <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>KL</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>1</v>
       </c>
-      <c r="I41" s="7">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8">
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
         <v>46087</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" s="7">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="7" t="s">
+      <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="7" t="str">
+      <c r="D42" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F42" s="7" t="str">
+      <c r="F42" t="str">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G42" s="7">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I42" s="7">
-        <v>2</v>
-      </c>
-      <c r="J42" s="8">
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42" s="4">
         <v>46092</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="5">
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="7">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="7" t="str">
+      <c r="D43" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
         <v>Basic</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
         <v>80</v>
       </c>
-      <c r="F43" s="7" t="str">
+      <c r="F43" t="str">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>NL</v>
       </c>
-      <c r="G43" s="7">
-        <v>0</v>
-      </c>
-      <c r="H43" s="7">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
         <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
         <v>0</v>
       </c>
-      <c r="I43" s="7">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8">
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
         <v>46112</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="5">
         <v>0.75</v>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J44" s="8"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J45" s="8"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J46" s="8"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J47" s="8"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J48" s="8"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-    </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J49" s="8"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-    </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J50" s="8"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-    </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J51" s="8"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-    </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J52" s="8"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-    </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J53" s="8"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-    </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J54" s="8"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J55" s="8"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-    </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J56" s="8"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-    </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J57" s="8"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-    </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J58" s="8"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-    </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J59" s="8"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-    </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J60" s="8"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-    </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J61" s="8"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-    </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J62" s="8"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J63" s="8"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J46" s="4"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J53" s="4"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2863,470 +2733,470 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3340,15 +3210,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2">
         <v>46082</v>
@@ -3444,7 +3322,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3542,12 +3420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3561,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3575,12 +3453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3678,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3776,12 +3654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3813,22 +3691,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3839,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3847,12 +3725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3860,12 +3738,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3915,17 +3793,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4023,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4034,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4132,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4152,7 +4030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4250,12 +4128,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4263,7 +4141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4274,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4288,17 +4166,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4333,7 +4211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4347,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4391,17 +4269,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4412,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4420,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4428,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4451,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4464,13 +4342,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4644,7 +4522,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4654,7 +4532,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4664,7 +4542,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4674,7 +4552,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4684,7 +4562,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4694,7 +4572,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4704,7 +4582,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4714,7 +4592,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4724,7 +4602,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4734,7 +4612,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4744,7 +4622,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4754,7 +4632,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4764,7 +4642,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4774,7 +4652,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4784,7 +4662,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4794,7 +4672,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4804,7 +4682,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4814,7 +4692,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4824,7 +4702,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4834,7 +4712,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4844,7 +4722,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4854,7 +4732,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4864,7 +4742,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4874,7 +4752,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4884,7 +4762,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4894,7 +4772,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4904,7 +4782,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4914,7 +4792,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4924,7 +4802,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4934,7 +4812,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4944,7 +4822,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4954,7 +4832,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4964,7 +4842,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4974,7 +4852,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4984,7 +4862,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4994,7 +4872,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -5004,7 +4882,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -5014,7 +4892,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -5024,17 +4902,17 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -5044,7 +4922,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -5054,7 +4932,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -5072,25 +4950,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5099,9 +4977,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5110,9 +4988,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5121,9 +4999,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -5132,9 +5010,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -5143,9 +5021,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5155,9 +5033,9 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5166,9 +5044,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5177,9 +5055,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5188,9 +5066,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5199,9 +5077,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5210,7 +5088,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5221,7 +5099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5232,7 +5110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5243,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5254,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5265,7 +5143,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5276,7 +5154,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5287,9 +5165,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5298,9 +5176,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5309,9 +5187,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5320,9 +5198,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5331,9 +5209,9 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5342,9 +5220,9 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5353,9 +5231,9 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5364,9 +5242,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5376,9 +5254,9 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5388,9 +5266,9 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5400,9 +5278,9 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5411,9 +5289,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5422,9 +5300,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5433,9 +5311,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5444,9 +5322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5455,9 +5333,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5466,9 +5344,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5485,25 +5363,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5514,7 +5392,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5525,7 +5403,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5536,7 +5414,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5547,7 +5425,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5558,7 +5436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5569,7 +5447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5580,7 +5458,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5591,7 +5469,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5608,337 +5486,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5956,18 +5521,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5979,12 +5544,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -6002,12 +5567,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -6025,12 +5590,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -6048,12 +5613,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -6071,12 +5636,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -6094,12 +5659,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -6117,18 +5682,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6140,12 +5705,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -6163,7 +5728,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6174,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6186,12 +5751,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6209,12 +5774,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -6232,12 +5797,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -6255,12 +5820,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6278,12 +5843,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D62F44-E08D-4066-B401-B3CA353F3FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E8118A-0AF3-634D-B88D-08E2D3D7F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16720" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -776,18 +776,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -910,7 +910,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -953,7 +953,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -995,7 +995,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="4">
-        <v>46095</v>
+        <v>46102</v>
       </c>
       <c r="K25" s="5">
         <v>0.75</v>
@@ -1847,7 +1847,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="K26" s="5">
         <v>0.75</v>
@@ -1890,23 +1890,23 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Barna</v>
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4">
-        <v>46109</v>
+        <v>46088</v>
       </c>
       <c r="K27" s="5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1956,7 +1956,6 @@
         <v>KL</v>
       </c>
       <c r="G28">
-        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H28">
@@ -1967,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>46088</v>
+        <v>46102</v>
       </c>
       <c r="K28" s="5">
         <v>0.5</v>
@@ -1976,7 +1975,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1999,6 +1998,7 @@
         <v>KL</v>
       </c>
       <c r="G29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2009,7 +2009,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="K29" s="5">
         <v>0.5</v>
@@ -2018,19 +2018,19 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>BL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2046,22 +2046,22 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>46109</v>
+        <v>46085</v>
       </c>
       <c r="K30" s="5">
-        <v>0.5</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L30" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="K31" s="5">
         <v>0.79166666666666663</v>
@@ -2104,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2127,7 +2127,6 @@
         <v>BL</v>
       </c>
       <c r="G32">
-        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H32">
@@ -2138,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="K32" s="5">
         <v>0.79166666666666663</v>
@@ -2147,7 +2146,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="K33" s="5">
         <v>0.79166666666666663</v>
@@ -2189,40 +2188,40 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="K34" s="5">
         <v>0.79166666666666663</v>
@@ -2231,15 +2230,15 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2247,24 +2246,24 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="K35" s="5">
         <v>0.79166666666666663</v>
@@ -2273,12 +2272,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -2303,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="K36" s="5">
         <v>0.79166666666666663</v>
@@ -2315,19 +2314,19 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2335,41 +2334,42 @@
       </c>
       <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4">
-        <v>46097</v>
+        <v>46103</v>
       </c>
       <c r="K37" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Basic</v>
       </c>
       <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2377,10 +2377,9 @@
       </c>
       <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>SB</v>
       </c>
       <c r="G38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H38">
@@ -2388,81 +2387,82 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4">
-        <v>46103</v>
+        <v>46107</v>
       </c>
       <c r="K38" s="5">
-        <v>0.5</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="L38" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>SB</v>
+        <v>NL</v>
       </c>
       <c r="G39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4">
-        <v>46107</v>
+        <v>46103</v>
       </c>
       <c r="K39" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="L39" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2470,30 +2470,30 @@
       </c>
       <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4">
-        <v>46103</v>
+        <v>46087</v>
       </c>
       <c r="K40" s="5">
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L40" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2501,25 +2501,24 @@
       </c>
       <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="4">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="K41" s="5">
         <v>0.79166666666666663</v>
@@ -2528,12 +2527,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -2558,159 +2557,117 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4">
-        <v>46092</v>
+        <v>46112</v>
       </c>
       <c r="K42" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="L42" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" s="4">
-        <v>46112</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L43" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J63" s="4"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2722,7 +2679,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C63</xm:sqref>
+          <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2733,14 +2690,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -2751,7 +2708,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2762,7 +2719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2773,7 +2730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2784,7 +2741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2795,7 +2752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2806,7 +2763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2817,7 +2774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2828,7 +2785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2839,7 +2796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2850,7 +2807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2861,7 +2818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2872,7 +2829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2883,7 +2840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2894,7 +2851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2905,7 +2862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2916,7 +2873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2927,7 +2884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2938,7 +2895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2949,7 +2906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2960,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2971,7 +2928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2982,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2993,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3004,7 +2961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3015,7 +2972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3026,7 +2983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3037,7 +2994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3048,7 +3005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3059,7 +3016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3070,7 +3027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3081,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3092,7 +3049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3103,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3114,7 +3071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3125,7 +3082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3136,7 +3093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3147,7 +3104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3158,7 +3115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3169,7 +3126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3180,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3191,7 +3148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3210,21 +3167,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3279,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3420,12 +3377,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3439,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3453,12 +3410,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3556,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3654,12 +3611,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3691,22 +3648,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3717,7 +3674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3725,12 +3682,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3738,12 +3695,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3793,17 +3750,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3901,7 +3858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3912,7 +3869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4010,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4030,7 +3987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4128,12 +4085,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4141,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4152,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4166,17 +4123,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4211,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4225,7 +4182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4269,17 +4226,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4290,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4298,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4306,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4329,7 +4286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4342,13 +4299,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4522,7 +4479,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4532,7 +4489,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4542,7 +4499,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4552,7 +4509,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4562,7 +4519,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4572,7 +4529,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4582,7 +4539,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4592,7 +4549,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4602,7 +4559,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4612,7 +4569,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4622,7 +4579,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4632,7 +4589,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4642,7 +4599,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4652,7 +4609,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4662,7 +4619,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4672,7 +4629,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4682,7 +4639,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4692,7 +4649,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4702,7 +4659,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4712,7 +4669,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4722,7 +4679,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4732,7 +4689,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4742,7 +4699,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4752,193 +4709,193 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B25" s="4" t="e">
+        <f>Events!#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
         <f>Events!B25</f>
         <v>HT</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B26" s="4">
         <f>Events!J25</f>
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="str">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
         <f>Events!B26</f>
         <v>HT</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B27" s="4">
         <f>Events!J26</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="str">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
         <f>Events!B27</f>
-        <v>HT</v>
-      </c>
-      <c r="B27" s="4">
+        <v>EÁ</v>
+      </c>
+      <c r="B28" s="4">
         <f>Events!J27</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="str">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B29" s="4">
         <f>Events!J28</f>
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="str">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B30" s="4">
         <f>Events!J29</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="str">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
         <f>Events!B30</f>
-        <v>EÁ</v>
-      </c>
-      <c r="B30" s="4">
+        <v>Múlinn</v>
+      </c>
+      <c r="B31" s="4">
         <f>Events!J30</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="str">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B32" s="4">
         <f>Events!J31</f>
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="str">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B33" s="4">
         <f>Events!J32</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="str">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B34" s="4">
         <f>Events!J33</f>
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="str">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
         <f>Events!B34</f>
-        <v>Múlinn</v>
-      </c>
-      <c r="B34" s="4">
+        <v>UR</v>
+      </c>
+      <c r="B35" s="4">
         <f>Events!J34</f>
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="str">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
         <f>Events!B35</f>
-        <v>UR</v>
-      </c>
-      <c r="B35" s="4">
+        <v>KD</v>
+      </c>
+      <c r="B36" s="4">
         <f>Events!J35</f>
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="str">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="str">
         <f>Events!B36</f>
-        <v>KD</v>
-      </c>
-      <c r="B36" s="4">
+        <v>JN</v>
+      </c>
+      <c r="B37" s="4">
         <f>Events!J36</f>
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="str">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="str">
         <f>Events!B37</f>
-        <v>JN</v>
-      </c>
-      <c r="B37" s="4">
+        <v>K&amp;B</v>
+      </c>
+      <c r="B38" s="4">
         <f>Events!J37</f>
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="str">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
         <f>Events!B38</f>
-        <v>K&amp;B</v>
-      </c>
-      <c r="B38" s="4">
+        <v>Svef</v>
+      </c>
+      <c r="B39" s="4">
         <f>Events!J38</f>
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>Events!B39</f>
+        <v>Sígildir</v>
+      </c>
+      <c r="B40" s="4">
+        <f>Events!J39</f>
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" t="str">
-        <f>Events!B39</f>
-        <v>Svef</v>
-      </c>
-      <c r="B39" s="4">
-        <f>Events!J39</f>
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" t="str">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
         <f>Events!B40</f>
-        <v>Sígildir</v>
-      </c>
-      <c r="B40" s="4">
+        <v>tón</v>
+      </c>
+      <c r="B41" s="4">
         <f>Events!J40</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" t="str">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
         <f>Events!B41</f>
-        <v>tón</v>
-      </c>
-      <c r="B41" s="4">
+        <v>ÖL</v>
+      </c>
+      <c r="B42" s="4">
         <f>Events!J41</f>
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" t="str">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
         <f>Events!B42</f>
-        <v>ÖL</v>
-      </c>
-      <c r="B42" s="4">
+        <v>RF</v>
+      </c>
+      <c r="B43" s="4">
         <f>Events!J42</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="str">
-        <f>Events!B43</f>
-        <v>RF</v>
-      </c>
-      <c r="B43" s="4">
-        <f>Events!J43</f>
         <v>46112</v>
       </c>
     </row>
@@ -4950,12 +4907,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4966,7 +4923,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -4977,7 +4934,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -4988,7 +4945,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4999,7 +4956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -5010,7 +4967,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -5021,7 +4978,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -5033,7 +4990,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -5044,7 +5001,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5066,7 +5023,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -5077,7 +5034,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5088,7 +5045,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5099,7 +5056,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5110,7 +5067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5121,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5132,7 +5089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5143,7 +5100,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5154,7 +5111,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5165,7 +5122,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -5176,7 +5133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -5187,7 +5144,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5198,7 +5155,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5209,7 +5166,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -5220,7 +5177,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -5231,7 +5188,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -5242,7 +5199,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -5254,7 +5211,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -5266,7 +5223,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -5278,7 +5235,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -5289,7 +5246,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5300,7 +5257,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -5311,7 +5268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -5322,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -5333,7 +5290,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -5344,7 +5301,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -5363,14 +5320,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5381,7 +5338,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5392,7 +5349,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5403,7 +5360,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5414,7 +5371,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5425,7 +5382,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5436,7 +5393,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5447,7 +5404,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5458,7 +5415,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5469,7 +5426,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5488,17 +5445,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5521,7 +5478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5544,7 +5501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5567,7 +5524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5590,7 +5547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5613,7 +5570,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5636,7 +5593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5659,7 +5616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5705,7 +5662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5728,7 +5685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5751,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5774,7 +5731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5797,7 +5754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5820,7 +5777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5843,7 +5800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E8118A-0AF3-634D-B88D-08E2D3D7F1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1241685D-86BE-A94A-A986-ED8F50A0DC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16720" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
+    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="151">
   <si>
     <t>Event</t>
   </si>
@@ -125,9 +126,123 @@
     <t>EventRanking</t>
   </si>
   <si>
+    <t>Mínus</t>
+  </si>
+  <si>
+    <t>Helgi, kominn með aðra helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú ert kominn með 4 helgar</t>
+  </si>
+  <si>
+    <t>Helgi, var með helgi síðast</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 1 helgi</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 2 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 3 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 4 helgar</t>
+  </si>
+  <si>
+    <t>Ef þú varst með 5 helgar</t>
+  </si>
+  <si>
+    <t>Salur</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
+  </si>
+  <si>
+    <t>Vika</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
+  </si>
+  <si>
+    <t>Hvað hún er löng</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
+  </si>
+  <si>
+    <t>Langar vaktir</t>
+  </si>
+  <si>
+    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
+  </si>
+  <si>
+    <t>Með hverjum?</t>
+  </si>
+  <si>
     <t>Skillset</t>
   </si>
   <si>
+    <t>Ef þarf skillset 2 en þú ert 1</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 en þú ert 3</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 2 og þú ert</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 og þú ert</t>
+  </si>
+  <si>
     <t>K&amp;B</t>
   </si>
   <si>
@@ -180,6 +295,12 @@
   </si>
   <si>
     <t>EmpSkillset</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 1 en þú ert ekki</t>
+  </si>
+  <si>
+    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
   <si>
     <t>Req_this_shift</t>
@@ -434,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -442,6 +563,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
@@ -798,7 +922,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -830,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -915,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -958,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -992,7 +1116,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L5" s="5">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1000,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1043,7 +1167,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1086,7 +1210,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1097,7 +1221,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1129,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
@@ -1301,7 +1425,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1344,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -1386,7 +1510,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
@@ -1429,7 +1553,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1472,7 +1596,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -1514,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -1556,7 +1680,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
@@ -1590,7 +1714,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L19" s="5">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -1598,7 +1722,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -1632,7 +1756,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L20" s="5">
-        <v>0.875</v>
+        <v>0.89583333333333337</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1640,7 +1764,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1682,7 +1806,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1724,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1766,7 +1890,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
         <v>2</v>
@@ -1809,7 +1933,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1838,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="4">
-        <v>46102</v>
+        <v>46095</v>
       </c>
       <c r="K25" s="5">
         <v>0.75</v>
@@ -1852,7 +1976,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -1881,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>46109</v>
+        <v>46102</v>
       </c>
       <c r="K26" s="5">
         <v>0.75</v>
@@ -1895,18 +2019,18 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1918,19 +2042,19 @@
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>46088</v>
+        <v>46109</v>
       </c>
       <c r="K27" s="5">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L27" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -1938,7 +2062,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
         <v>16</v>
@@ -1956,6 +2080,7 @@
         <v>KL</v>
       </c>
       <c r="G28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H28">
@@ -1966,7 +2091,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>46102</v>
+        <v>46088</v>
       </c>
       <c r="K28" s="5">
         <v>0.5</v>
@@ -1975,12 +2100,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -1998,7 +2123,6 @@
         <v>KL</v>
       </c>
       <c r="G29">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2009,7 +2133,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46109</v>
+        <v>46102</v>
       </c>
       <c r="K29" s="5">
         <v>0.5</v>
@@ -2018,19 +2142,19 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Barna</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2038,7 +2162,7 @@
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2046,19 +2170,19 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="4">
-        <v>46085</v>
+        <v>46109</v>
       </c>
       <c r="K30" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="5">
-        <v>0.91666666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2077,7 +2201,7 @@
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2095,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="K31" s="5">
         <v>0.79166666666666663</v>
@@ -2120,13 +2244,14 @@
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
         <v>BL</v>
       </c>
       <c r="G32">
+        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H32">
@@ -2137,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="K32" s="5">
         <v>0.79166666666666663</v>
@@ -2146,7 +2271,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2162,7 +2287,7 @@
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2179,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="K33" s="5">
         <v>0.79166666666666663</v>
@@ -2193,35 +2318,35 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>BL</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>46091</v>
+        <v>46106</v>
       </c>
       <c r="K34" s="5">
         <v>0.79166666666666663</v>
@@ -2235,10 +2360,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2246,24 +2371,24 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="4">
-        <v>46098</v>
+        <v>46091</v>
       </c>
       <c r="K35" s="5">
         <v>0.79166666666666663</v>
@@ -2277,7 +2402,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -2302,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="K36" s="5">
         <v>0.79166666666666663</v>
@@ -2319,14 +2444,14 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Basic</v>
       </c>
       <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2334,27 +2459,26 @@
       </c>
       <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="4">
-        <v>46103</v>
+        <v>46097</v>
       </c>
       <c r="K37" s="5">
-        <v>0.5</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L37" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -2362,14 +2486,14 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2377,9 +2501,10 @@
       </c>
       <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>SB</v>
+        <v>KL</v>
       </c>
       <c r="G38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H38">
@@ -2387,16 +2512,16 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="4">
-        <v>46107</v>
+        <v>46103</v>
       </c>
       <c r="K38" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="5">
-        <v>0.83333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -2404,42 +2529,41 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>SB</v>
       </c>
       <c r="G39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" s="4">
-        <v>46103</v>
+        <v>46107</v>
       </c>
       <c r="K39" s="5">
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="L39" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -2447,22 +2571,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2470,19 +2594,19 @@
       </c>
       <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4">
-        <v>46087</v>
+        <v>46096</v>
       </c>
       <c r="K40" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="L40" s="5">
         <v>0.79166666666666663</v>
-      </c>
-      <c r="L40" s="5">
-        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2490,10 +2614,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2501,24 +2625,25 @@
       </c>
       <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="4">
-        <v>46092</v>
+        <v>46087</v>
       </c>
       <c r="K41" s="5">
         <v>0.79166666666666663</v>
@@ -2532,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -2557,22 +2682,59 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4">
+        <v>46092</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>NL</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
         <v>46112</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K43" s="5">
         <v>0.75</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L43" s="5">
         <v>0.875</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J43" s="4"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J44" s="4"/>
@@ -2668,6 +2830,11 @@
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2679,7 +2846,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C62</xm:sqref>
+          <xm:sqref>C2:C63</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2699,13 +2866,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2713,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2724,7 +2891,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2735,7 +2902,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -2746,7 +2913,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -2757,7 +2924,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -2768,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2779,7 +2946,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2790,7 +2957,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2801,7 +2968,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2812,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2823,7 +2990,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2834,7 +3001,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -2845,7 +3012,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2856,7 +3023,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -2867,7 +3034,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2878,7 +3045,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2889,7 +3056,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2900,7 +3067,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -2911,7 +3078,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -2922,7 +3089,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2933,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2944,7 +3111,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -2955,7 +3122,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2966,7 +3133,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2977,7 +3144,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2988,7 +3155,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -2999,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -3010,7 +3177,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -3021,7 +3188,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -3032,7 +3199,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -3043,7 +3210,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -3054,7 +3221,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -3065,7 +3232,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -3076,7 +3243,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -3087,7 +3254,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -3098,7 +3265,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3109,7 +3276,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -3120,7 +3287,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3131,7 +3298,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -3142,7 +3309,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -3153,7 +3320,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3170,20 +3337,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2">
         <v>46082</v>
@@ -4710,192 +4869,192 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B25" s="4" t="e">
-        <f>Events!#REF!</f>
-        <v>#REF!</v>
+      <c r="A25" t="str">
+        <f>Events!B25</f>
+        <v>HT</v>
+      </c>
+      <c r="B25" s="4">
+        <f>Events!J25</f>
+        <v>46095</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <f>Events!B25</f>
+        <f>Events!B26</f>
         <v>HT</v>
       </c>
       <c r="B26" s="4">
-        <f>Events!J25</f>
+        <f>Events!J26</f>
         <v>46102</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>Events!B26</f>
+        <f>Events!B27</f>
         <v>HT</v>
       </c>
       <c r="B27" s="4">
-        <f>Events!J26</f>
+        <f>Events!J27</f>
         <v>46109</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <f>Events!B27</f>
+        <f>Events!B28</f>
         <v>EÁ</v>
       </c>
       <c r="B28" s="4">
-        <f>Events!J27</f>
+        <f>Events!J28</f>
         <v>46088</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <f>Events!B28</f>
+        <f>Events!B29</f>
         <v>EÁ</v>
       </c>
       <c r="B29" s="4">
-        <f>Events!J28</f>
+        <f>Events!J29</f>
         <v>46102</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <f>Events!B29</f>
+        <f>Events!B30</f>
         <v>EÁ</v>
       </c>
       <c r="B30" s="4">
-        <f>Events!J29</f>
+        <f>Events!J30</f>
         <v>46109</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <f>Events!B30</f>
+        <f>Events!B31</f>
         <v>Múlinn</v>
       </c>
       <c r="B31" s="4">
-        <f>Events!J30</f>
+        <f>Events!J31</f>
         <v>46085</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <f>Events!B31</f>
+        <f>Events!B32</f>
         <v>Múlinn</v>
       </c>
       <c r="B32" s="4">
-        <f>Events!J31</f>
+        <f>Events!J32</f>
         <v>46092</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <f>Events!B32</f>
+        <f>Events!B33</f>
         <v>Múlinn</v>
       </c>
       <c r="B33" s="4">
-        <f>Events!J32</f>
+        <f>Events!J33</f>
         <v>46099</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <f>Events!B33</f>
+        <f>Events!B34</f>
         <v>Múlinn</v>
       </c>
       <c r="B34" s="4">
-        <f>Events!J33</f>
+        <f>Events!J34</f>
         <v>46106</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <f>Events!B34</f>
+        <f>Events!B35</f>
         <v>UR</v>
       </c>
       <c r="B35" s="4">
-        <f>Events!J34</f>
+        <f>Events!J35</f>
         <v>46091</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <f>Events!B35</f>
+        <f>Events!B36</f>
         <v>KD</v>
       </c>
       <c r="B36" s="4">
-        <f>Events!J35</f>
+        <f>Events!J36</f>
         <v>46098</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <f>Events!B36</f>
+        <f>Events!B37</f>
         <v>JN</v>
       </c>
       <c r="B37" s="4">
-        <f>Events!J36</f>
+        <f>Events!J37</f>
         <v>46097</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <f>Events!B37</f>
+        <f>Events!B38</f>
         <v>K&amp;B</v>
       </c>
       <c r="B38" s="4">
-        <f>Events!J37</f>
+        <f>Events!J38</f>
         <v>46103</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <f>Events!B38</f>
+        <f>Events!B39</f>
         <v>Svef</v>
       </c>
       <c r="B39" s="4">
-        <f>Events!J38</f>
+        <f>Events!J39</f>
         <v>46107</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <f>Events!B39</f>
+        <f>Events!B40</f>
         <v>Sígildir</v>
       </c>
       <c r="B40" s="4">
-        <f>Events!J39</f>
-        <v>46103</v>
+        <f>Events!J40</f>
+        <v>46096</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <f>Events!B40</f>
+        <f>Events!B41</f>
         <v>tón</v>
       </c>
       <c r="B41" s="4">
-        <f>Events!J40</f>
+        <f>Events!J41</f>
         <v>46087</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
-        <f>Events!B41</f>
+        <f>Events!B42</f>
         <v>ÖL</v>
       </c>
       <c r="B42" s="4">
-        <f>Events!J41</f>
+        <f>Events!J42</f>
         <v>46092</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
-        <f>Events!B42</f>
+        <f>Events!B43</f>
         <v>RF</v>
       </c>
       <c r="B43" s="4">
-        <f>Events!J42</f>
+        <f>Events!J43</f>
         <v>46112</v>
       </c>
     </row>
@@ -4914,18 +5073,18 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4936,7 +5095,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -4947,7 +5106,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -4958,7 +5117,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -4969,7 +5128,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -4980,7 +5139,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -4992,7 +5151,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5003,7 +5162,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5014,7 +5173,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5025,7 +5184,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5036,7 +5195,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5124,7 +5283,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5135,7 +5294,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5146,7 +5305,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5157,7 +5316,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5168,7 +5327,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5179,7 +5338,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5190,7 +5349,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5201,7 +5360,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5213,7 +5372,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5225,7 +5384,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5237,7 +5396,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5248,7 +5407,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5259,7 +5418,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5270,7 +5429,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5281,7 +5440,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5292,7 +5451,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5303,7 +5462,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5329,13 +5488,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -5443,6 +5602,319 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
+  <dimension ref="A1:C41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <f>+C20*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22">
+        <f>+C21*2</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <f>+C22*2</f>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24">
+        <f>+C23*2</f>
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27">
+        <f>+C26*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <f>+C27*2</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <f>+C28*2</f>
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41">
+        <v>-200</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5460,7 +5932,7 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5483,13 +5955,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5506,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -5529,7 +6001,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -5552,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -5575,7 +6047,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -5598,7 +6070,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -5621,7 +6093,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -5644,13 +6116,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5667,7 +6139,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -5696,7 +6168,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5713,7 +6185,7 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -5736,7 +6208,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -5759,7 +6231,7 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -5782,7 +6254,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -5805,7 +6277,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1241685D-86BE-A94A-A986-ED8F50A0DC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CDB1FB2-C71F-4021-9F2C-FCA963A4F22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="EventReq" sheetId="9" r:id="rId4"/>
     <sheet name="ScoreKeys" sheetId="7" r:id="rId5"/>
     <sheet name="SkillsetScores" sheetId="8" r:id="rId6"/>
-    <sheet name="Score krass" sheetId="6" r:id="rId7"/>
-    <sheet name="EventTypes" sheetId="5" r:id="rId8"/>
+    <sheet name="EventTypes" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -126,123 +125,9 @@
     <t>EventRanking</t>
   </si>
   <si>
-    <t>Mínus</t>
-  </si>
-  <si>
-    <t>Helgi, kominn með aðra helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert ekki kominn með neina vakt um helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú ert kominn með 4 helgar</t>
-  </si>
-  <si>
-    <t>Helgi, var með helgi síðast</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 1 helgi</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 2 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 3 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 4 helgar</t>
-  </si>
-  <si>
-    <t>Ef þú varst með 5 helgar</t>
-  </si>
-  <si>
-    <t>Salur</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessum sal á tímabilinu</t>
-  </si>
-  <si>
-    <t>Vika</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 5 vaktir í þessari viku</t>
-  </si>
-  <si>
-    <t>Hvað hún er löng</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 1 vakt með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 2 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 3 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá 4 vaktir með þessa lengd</t>
-  </si>
-  <si>
-    <t>Langar vaktir</t>
-  </si>
-  <si>
-    <t>Ef þú ert búinn að fá vakt á þessu tímabili sem er lengri en 6 klst.</t>
-  </si>
-  <si>
-    <t>Með hverjum?</t>
-  </si>
-  <si>
     <t>Skillset</t>
   </si>
   <si>
-    <t>Ef þarf skillset 2 en þú ert 1</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 en þú ert 3</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 2 og þú ert</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 og þú ert</t>
-  </si>
-  <si>
     <t>K&amp;B</t>
   </si>
   <si>
@@ -295,12 +180,6 @@
   </si>
   <si>
     <t>EmpSkillset</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 1 en þú ert ekki</t>
-  </si>
-  <si>
-    <t>Ef þarf skillset 3 og þú ert 1 eða 2</t>
   </si>
   <si>
     <t>Req_this_shift</t>
@@ -555,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -563,9 +442,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,17 +777,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -922,7 +798,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -949,12 +825,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -992,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1034,12 +910,12 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -1077,12 +953,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1116,15 +992,15 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L5" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1162,12 +1038,12 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
@@ -1205,12 +1081,12 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -1221,7 +1097,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1248,12 +1124,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
@@ -1292,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1335,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1378,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1420,12 +1296,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1463,12 +1339,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -1505,12 +1381,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
@@ -1548,12 +1424,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1591,12 +1467,12 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
@@ -1633,12 +1509,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -1675,12 +1551,12 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
@@ -1714,15 +1590,15 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L19" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
@@ -1756,15 +1632,15 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="L20" s="5">
-        <v>0.89583333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
@@ -1801,12 +1677,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1843,12 +1719,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1885,12 +1761,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
         <v>2</v>
@@ -1928,12 +1804,12 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -1971,12 +1847,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -2014,12 +1890,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -2057,12 +1933,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
         <v>16</v>
@@ -2100,12 +1976,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -2142,12 +2018,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
         <v>16</v>
@@ -2185,7 +2061,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2201,7 +2077,7 @@
       </c>
       <c r="E31">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F31" t="str">
         <f>_xlfn.XLOOKUP(C31,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2228,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2244,7 +2120,7 @@
       </c>
       <c r="E32">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F32" t="str">
         <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2271,7 +2147,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2287,7 +2163,7 @@
       </c>
       <c r="E33">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F33" t="str">
         <f>_xlfn.XLOOKUP(C33,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2313,7 +2189,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2329,7 +2205,7 @@
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2355,12 +2231,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -2397,12 +2273,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -2439,12 +2315,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>6</v>
@@ -2481,12 +2357,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
@@ -2524,12 +2400,12 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -2566,7 +2442,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2582,7 +2458,7 @@
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -2600,7 +2476,7 @@
         <v>2</v>
       </c>
       <c r="J40" s="4">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="K40" s="5">
         <v>0.625</v>
@@ -2609,12 +2485,12 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -2652,12 +2528,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -2694,12 +2570,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
@@ -2736,102 +2612,102 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J63" s="4"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
@@ -2857,470 +2733,470 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -3334,15 +3210,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="32" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2">
         <v>46082</v>
@@ -3438,7 +3322,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3536,12 +3420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3555,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3569,12 +3453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3672,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3770,12 +3654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3807,22 +3691,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3833,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3841,12 +3725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3854,12 +3738,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3909,17 +3793,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4017,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4028,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4126,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4146,7 +4030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4244,12 +4128,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4257,7 +4141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4268,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4282,17 +4166,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4327,7 +4211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4341,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4385,17 +4269,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4406,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4414,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4422,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4445,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4458,13 +4342,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4638,7 +4522,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4648,7 +4532,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4658,7 +4542,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4668,7 +4552,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4678,7 +4562,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4688,7 +4572,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4698,7 +4582,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4708,7 +4592,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4718,7 +4602,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4728,7 +4612,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4738,7 +4622,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4748,7 +4632,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4758,7 +4642,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4768,7 +4652,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4778,7 +4662,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4788,7 +4672,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4798,7 +4682,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4808,7 +4692,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4818,7 +4702,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4828,7 +4712,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4838,7 +4722,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4848,7 +4732,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4858,7 +4742,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4868,7 +4752,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4878,7 +4762,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4888,7 +4772,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4898,7 +4782,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4908,7 +4792,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4918,7 +4802,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4928,7 +4812,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4938,7 +4822,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4948,7 +4832,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4958,7 +4842,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4968,7 +4852,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4978,7 +4862,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4988,7 +4872,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -4998,7 +4882,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -5008,7 +4892,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -5018,17 +4902,17 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -5038,7 +4922,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -5048,7 +4932,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -5066,25 +4950,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5093,9 +4977,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -5104,9 +4988,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5115,9 +4999,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -5126,9 +5010,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -5137,9 +5021,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -5149,9 +5033,9 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -5160,9 +5044,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -5171,9 +5055,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -5182,9 +5066,9 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -5193,9 +5077,9 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -5204,7 +5088,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5215,7 +5099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5226,7 +5110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5237,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5248,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5259,7 +5143,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5270,7 +5154,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5281,9 +5165,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -5292,9 +5176,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5303,9 +5187,9 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5314,9 +5198,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -5325,9 +5209,9 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -5336,9 +5220,9 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>5</v>
@@ -5347,9 +5231,9 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -5358,9 +5242,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5370,9 +5254,9 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -5382,9 +5266,9 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -5394,9 +5278,9 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5405,20 +5289,20 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -5427,9 +5311,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5438,9 +5322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5449,9 +5333,9 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -5460,9 +5344,9 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -5479,25 +5363,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5505,10 +5389,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5516,10 +5400,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5530,7 +5414,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5541,7 +5425,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5552,7 +5436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5563,7 +5447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5574,7 +5458,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5585,7 +5469,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5602,337 +5486,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4BFCF1-DD02-4616-AA4A-3FD405A6C41D}">
-  <dimension ref="A1:C41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <f>+C20*2</f>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22">
-        <f>+C21*2</f>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23">
-        <f>+C22*2</f>
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24">
-        <f>+C23*2</f>
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27">
-        <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28">
-        <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41">
-        <v>-200</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5950,18 +5521,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5973,12 +5544,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -5996,12 +5567,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -6019,12 +5590,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -6042,12 +5613,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -6065,12 +5636,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -6088,12 +5659,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -6111,18 +5682,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6134,12 +5705,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
@@ -6157,7 +5728,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6168,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6180,12 +5751,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -6203,12 +5774,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -6226,12 +5797,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
@@ -6249,12 +5820,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -6272,12 +5843,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CDB1FB2-C71F-4021-9F2C-FCA963A4F22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86493E4-2829-C642-B660-AF58891A0C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16720" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -776,18 +776,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -884,7 +884,7 @@
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -910,7 +910,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -926,7 +926,7 @@
       </c>
       <c r="E4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -953,7 +953,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -980,7 +980,7 @@
       </c>
       <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -995,7 +995,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1038,7 +1038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1124,7 +1124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1211,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1254,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1296,7 +1296,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1339,7 +1339,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1467,7 +1467,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1509,7 +1509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -1551,7 +1551,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -1593,7 +1593,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -1677,7 +1677,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1761,7 +1761,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="4">
-        <v>46095</v>
+        <v>46102</v>
       </c>
       <c r="K25" s="5">
         <v>0.75</v>
@@ -1847,7 +1847,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="K26" s="5">
         <v>0.75</v>
@@ -1890,23 +1890,23 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Barna</v>
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="4">
-        <v>46109</v>
+        <v>46088</v>
       </c>
       <c r="K27" s="5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1956,7 +1956,6 @@
         <v>KL</v>
       </c>
       <c r="G28">
-        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H28">
@@ -1967,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>46088</v>
+        <v>46102</v>
       </c>
       <c r="K28" s="5">
         <v>0.5</v>
@@ -1976,7 +1975,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1999,6 +1998,7 @@
         <v>KL</v>
       </c>
       <c r="G29">
+        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2009,7 +2009,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="K29" s="5">
         <v>0.5</v>
@@ -2018,19 +2018,19 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>BL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2046,22 +2046,22 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" s="4">
-        <v>46109</v>
+        <v>46085</v>
       </c>
       <c r="K30" s="5">
-        <v>0.5</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L30" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="K31" s="5">
         <v>0.79166666666666663</v>
@@ -2104,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2127,7 +2127,6 @@
         <v>BL</v>
       </c>
       <c r="G32">
-        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H32">
@@ -2138,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="K32" s="5">
         <v>0.79166666666666663</v>
@@ -2147,7 +2146,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2180,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="K33" s="5">
         <v>0.79166666666666663</v>
@@ -2189,19 +2188,19 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2209,20 +2208,20 @@
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>46106</v>
+        <v>46091</v>
       </c>
       <c r="K34" s="5">
         <v>0.79166666666666663</v>
@@ -2231,15 +2230,15 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2247,11 +2246,11 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2261,10 +2260,10 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="4">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="K35" s="5">
         <v>0.79166666666666663</v>
@@ -2273,12 +2272,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -2300,13 +2299,13 @@
       </c>
       <c r="H36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="K36" s="5">
         <v>0.79166666666666663</v>
@@ -2315,19 +2314,19 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2335,41 +2334,42 @@
       </c>
       <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G37">
+        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="4">
-        <v>46097</v>
+        <v>46103</v>
       </c>
       <c r="K37" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Basic</v>
       </c>
       <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2377,10 +2377,9 @@
       </c>
       <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>SB</v>
       </c>
       <c r="G38">
-        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H38">
@@ -2388,81 +2387,82 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="4">
-        <v>46103</v>
+        <v>46107</v>
       </c>
       <c r="K38" s="5">
-        <v>0.5</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="L38" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>SB</v>
+        <v>NL</v>
       </c>
       <c r="G39">
+        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4">
-        <v>46107</v>
+        <v>46103</v>
       </c>
       <c r="K39" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="L39" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2470,30 +2470,30 @@
       </c>
       <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="4">
-        <v>46103</v>
+        <v>46087</v>
       </c>
       <c r="K40" s="5">
-        <v>0.625</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L40" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2501,14 +2501,13 @@
       </c>
       <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G41">
-        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H41">
@@ -2516,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="4">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="K41" s="5">
         <v>0.79166666666666663</v>
@@ -2528,12 +2527,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -2555,162 +2554,120 @@
       </c>
       <c r="H42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="4">
-        <v>46092</v>
+        <v>46112</v>
       </c>
       <c r="K42" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="L42" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
-      </c>
-      <c r="E43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
-      </c>
-      <c r="F43" t="str">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43" s="4">
-        <v>46112</v>
-      </c>
-      <c r="K43" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="L43" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
-    </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J63" s="4"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2722,7 +2679,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C63</xm:sqref>
+          <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2733,14 +2690,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -2751,7 +2708,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2762,7 +2719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2773,7 +2730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2784,7 +2741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2795,7 +2752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2806,7 +2763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2817,7 +2774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2828,7 +2785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2839,7 +2796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2850,7 +2807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2861,7 +2818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2872,7 +2829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2883,7 +2840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2894,7 +2851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2905,7 +2862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2916,7 +2873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2927,7 +2884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2938,7 +2895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2949,7 +2906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2960,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2971,7 +2928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2982,7 +2939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2993,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3004,7 +2961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3015,7 +2972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3026,7 +2983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3037,7 +2994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3048,7 +3005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3059,7 +3016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3070,7 +3027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3081,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3092,7 +3049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3103,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3114,7 +3071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3125,7 +3082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3136,7 +3093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3147,7 +3104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3158,7 +3115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3169,7 +3126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3180,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3191,7 +3148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3210,21 +3167,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3279,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3420,12 +3377,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3439,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3453,12 +3410,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3556,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3654,12 +3611,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3691,22 +3648,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3717,7 +3674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3725,12 +3682,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3738,12 +3695,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3793,17 +3750,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3901,7 +3858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3912,7 +3869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4010,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4030,7 +3987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4128,12 +4085,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4141,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4152,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4166,17 +4123,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4211,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4225,7 +4182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4269,17 +4226,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4290,7 +4247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4298,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4306,7 +4263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4329,7 +4286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4341,14 +4298,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
-  <dimension ref="A1:AQ43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AQ42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4522,7 +4479,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4532,7 +4489,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4542,7 +4499,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4552,7 +4509,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4562,7 +4519,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4572,7 +4529,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4582,7 +4539,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4592,7 +4549,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4602,7 +4559,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4612,7 +4569,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4622,7 +4579,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4632,7 +4589,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4642,7 +4599,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4652,7 +4609,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4662,7 +4619,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4672,7 +4629,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4682,7 +4639,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4692,7 +4649,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4702,7 +4659,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4712,7 +4669,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4722,7 +4679,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4732,7 +4689,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4742,7 +4699,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4752,193 +4709,183 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
       </c>
       <c r="B25" s="4">
         <f>Events!J25</f>
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
       </c>
       <c r="B26" s="4">
         <f>Events!J26</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>Events!B27</f>
-        <v>HT</v>
+        <v>EÁ</v>
       </c>
       <c r="B27" s="4">
         <f>Events!J27</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
       </c>
       <c r="B28" s="4">
         <f>Events!J28</f>
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
       </c>
       <c r="B29" s="4">
         <f>Events!J29</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>Events!B30</f>
-        <v>EÁ</v>
+        <v>Múlinn</v>
       </c>
       <c r="B30" s="4">
         <f>Events!J30</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
       </c>
       <c r="B31" s="4">
         <f>Events!J31</f>
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
       </c>
       <c r="B32" s="4">
         <f>Events!J32</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
       </c>
       <c r="B33" s="4">
         <f>Events!J33</f>
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f>Events!B34</f>
-        <v>Múlinn</v>
+        <v>UR</v>
       </c>
       <c r="B34" s="4">
         <f>Events!J34</f>
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f>Events!B35</f>
-        <v>UR</v>
+        <v>KD</v>
       </c>
       <c r="B35" s="4">
         <f>Events!J35</f>
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>Events!B36</f>
-        <v>KD</v>
+        <v>JN</v>
       </c>
       <c r="B36" s="4">
         <f>Events!J36</f>
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>Events!B37</f>
-        <v>JN</v>
+        <v>K&amp;B</v>
       </c>
       <c r="B37" s="4">
         <f>Events!J37</f>
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
         <f>Events!B38</f>
-        <v>K&amp;B</v>
+        <v>Svef</v>
       </c>
       <c r="B38" s="4">
         <f>Events!J38</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>Events!B39</f>
-        <v>Svef</v>
+        <v>Sígildir</v>
       </c>
       <c r="B39" s="4">
         <f>Events!J39</f>
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f>Events!B40</f>
-        <v>Sígildir</v>
+        <v>tón</v>
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f>Events!B41</f>
-        <v>tón</v>
+        <v>ÖL</v>
       </c>
       <c r="B41" s="4">
         <f>Events!J41</f>
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
         <f>Events!B42</f>
-        <v>ÖL</v>
+        <v>RF</v>
       </c>
       <c r="B42" s="4">
         <f>Events!J42</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" t="str">
-        <f>Events!B43</f>
-        <v>RF</v>
-      </c>
-      <c r="B43" s="4">
-        <f>Events!J43</f>
         <v>46112</v>
       </c>
     </row>
@@ -4950,12 +4897,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4966,7 +4913,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -4977,7 +4924,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -4988,7 +4935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4999,7 +4946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -5010,7 +4957,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -5021,7 +4968,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -5033,7 +4980,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -5044,7 +4991,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5066,7 +5013,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -5077,7 +5024,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5088,7 +5035,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5099,7 +5046,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5110,7 +5057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5121,7 +5068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5132,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5143,7 +5090,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5154,7 +5101,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5165,7 +5112,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -5176,7 +5123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -5187,7 +5134,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5198,7 +5145,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5209,7 +5156,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -5220,7 +5167,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -5231,7 +5178,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -5242,7 +5189,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -5254,7 +5201,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -5266,7 +5213,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -5278,7 +5225,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -5289,7 +5236,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5297,10 +5244,10 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -5311,7 +5258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -5322,7 +5269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -5333,7 +5280,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -5344,7 +5291,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -5363,14 +5310,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5381,7 +5328,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5389,10 +5336,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5400,10 +5347,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-10000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5414,7 +5361,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5425,7 +5372,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5436,7 +5383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5447,7 +5394,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5458,7 +5405,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5469,7 +5416,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5488,17 +5435,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5521,7 +5468,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5544,7 +5491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5567,7 +5514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5590,7 +5537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5601,7 +5548,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5613,7 +5560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5636,7 +5583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5659,7 +5606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5705,7 +5652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5716,7 +5663,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5728,7 +5675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5739,7 +5686,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5751,7 +5698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5774,7 +5721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5785,7 +5732,7 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5797,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5808,7 +5755,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5820,7 +5767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5834,16 +5781,16 @@
         <v>80</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86493E4-2829-C642-B660-AF58891A0C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8012448-62C7-440D-8B04-E5A2D25F4758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26240" windowHeight="16720" activeTab="3" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -776,18 +776,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
-  <dimension ref="A1:L62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L63"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="9" max="11" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -884,7 +884,7 @@
       </c>
       <c r="E3">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F3" t="str">
         <f>_xlfn.XLOOKUP(C3,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -910,7 +910,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -926,7 +926,7 @@
       </c>
       <c r="E4">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F4" t="str">
         <f>_xlfn.XLOOKUP(C4,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -953,7 +953,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -980,7 +980,7 @@
       </c>
       <c r="H5">
         <f>_xlfn.XLOOKUP(C5,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -995,7 +995,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E6">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F6" t="str">
         <f>_xlfn.XLOOKUP(C6,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1038,7 +1038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E8">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.XLOOKUP(C8,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1124,7 +1124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E10">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F10" t="str">
         <f>_xlfn.XLOOKUP(C10,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1211,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="E11">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F11" t="str">
         <f>_xlfn.XLOOKUP(C11,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1254,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H12">
         <f>_xlfn.XLOOKUP(C12,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1296,7 +1296,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E13">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F13" t="str">
         <f>_xlfn.XLOOKUP(C13,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1339,7 +1339,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="E16">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F16" t="str">
         <f>_xlfn.XLOOKUP(C16,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1467,7 +1467,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H17">
         <f>_xlfn.XLOOKUP(C17,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -1509,7 +1509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H18">
         <f>_xlfn.XLOOKUP(C18,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -1551,7 +1551,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H19">
         <f>_xlfn.XLOOKUP(C19,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -1593,7 +1593,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H20">
         <f>_xlfn.XLOOKUP(C20,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1635,7 +1635,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H21">
         <f>_xlfn.XLOOKUP(C21,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -1677,7 +1677,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E22">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.XLOOKUP(C22,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E23">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F23" t="str">
         <f>_xlfn.XLOOKUP(C23,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1761,7 +1761,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="4">
-        <v>46102</v>
+        <v>46095</v>
       </c>
       <c r="K25" s="5">
         <v>0.75</v>
@@ -1847,7 +1847,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4">
-        <v>46109</v>
+        <v>46102</v>
       </c>
       <c r="K26" s="5">
         <v>0.75</v>
@@ -1890,23 +1890,23 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Solo</v>
       </c>
       <c r="E27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F27" t="str">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!C:C,"")</f>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="H27">
         <f>_xlfn.XLOOKUP(C27,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="4">
-        <v>46088</v>
+        <v>46109</v>
       </c>
       <c r="K27" s="5">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L27" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1956,6 +1956,7 @@
         <v>KL</v>
       </c>
       <c r="G28">
+        <f>_xlfn.XLOOKUP(C28,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H28">
@@ -1966,7 +1967,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="4">
-        <v>46102</v>
+        <v>46088</v>
       </c>
       <c r="K28" s="5">
         <v>0.5</v>
@@ -1975,7 +1976,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1998,7 +1999,6 @@
         <v>KL</v>
       </c>
       <c r="G29">
-        <f>_xlfn.XLOOKUP(C29,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H29">
@@ -2009,7 +2009,7 @@
         <v>2</v>
       </c>
       <c r="J29" s="4">
-        <v>46109</v>
+        <v>46102</v>
       </c>
       <c r="K29" s="5">
         <v>0.5</v>
@@ -2018,19 +2018,19 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Barna</v>
       </c>
       <c r="E30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="F30" t="str">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>BL</v>
+        <v>KL</v>
       </c>
       <c r="G30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2046,22 +2046,22 @@
       </c>
       <c r="H30">
         <f>_xlfn.XLOOKUP(C30,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="4">
-        <v>46085</v>
+        <v>46109</v>
       </c>
       <c r="K30" s="5">
-        <v>0.79166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="4">
-        <v>46092</v>
+        <v>46085</v>
       </c>
       <c r="K31" s="5">
         <v>0.79166666666666663</v>
@@ -2104,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2127,6 +2127,7 @@
         <v>BL</v>
       </c>
       <c r="G32">
+        <f>_xlfn.XLOOKUP(C32,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H32">
@@ -2137,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="4">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="K32" s="5">
         <v>0.79166666666666663</v>
@@ -2146,7 +2147,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2179,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="K33" s="5">
         <v>0.79166666666666663</v>
@@ -2188,19 +2189,19 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2208,20 +2209,20 @@
       </c>
       <c r="F34" t="str">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>BL</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
         <f>_xlfn.XLOOKUP(C34,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>1</v>
       </c>
       <c r="J34" s="4">
-        <v>46091</v>
+        <v>46106</v>
       </c>
       <c r="K34" s="5">
         <v>0.79166666666666663</v>
@@ -2230,15 +2231,15 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2246,11 +2247,11 @@
       </c>
       <c r="E35">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F35" t="str">
         <f>_xlfn.XLOOKUP(C35,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2260,10 +2261,10 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="4">
-        <v>46098</v>
+        <v>46091</v>
       </c>
       <c r="K35" s="5">
         <v>0.79166666666666663</v>
@@ -2272,12 +2273,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -2299,13 +2300,13 @@
       </c>
       <c r="H36">
         <f>_xlfn.XLOOKUP(C36,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="K36" s="5">
         <v>0.79166666666666663</v>
@@ -2314,19 +2315,19 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Barna</v>
+        <v>Basic</v>
       </c>
       <c r="E37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2334,42 +2335,41 @@
       </c>
       <c r="F37" t="str">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G37">
-        <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H37">
         <f>_xlfn.XLOOKUP(C37,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="4">
-        <v>46103</v>
+        <v>46097</v>
       </c>
       <c r="K37" s="5">
-        <v>0.5</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="L37" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Barna</v>
       </c>
       <c r="E38">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!D:D,"")</f>
@@ -2377,9 +2377,10 @@
       </c>
       <c r="F38" t="str">
         <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>SB</v>
+        <v>KL</v>
       </c>
       <c r="G38">
+        <f>_xlfn.XLOOKUP(C38,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H38">
@@ -2387,82 +2388,81 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="4">
-        <v>46107</v>
+        <v>46103</v>
       </c>
       <c r="K38" s="5">
-        <v>0.70833333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Solo</v>
+        <v>Basic</v>
       </c>
       <c r="E39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F39" t="str">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>SB</v>
       </c>
       <c r="G39">
-        <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H39">
         <f>_xlfn.XLOOKUP(C39,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" s="4">
-        <v>46103</v>
+        <v>46107</v>
       </c>
       <c r="K39" s="5">
-        <v>0.625</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="L39" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!B:B,"")</f>
-        <v>Basic</v>
+        <v>Solo</v>
       </c>
       <c r="E40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F40" t="str">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>KL</v>
+        <v>NL</v>
       </c>
       <c r="G40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!E:E,"")</f>
@@ -2470,30 +2470,30 @@
       </c>
       <c r="H40">
         <f>_xlfn.XLOOKUP(C40,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4">
-        <v>46087</v>
+        <v>46103</v>
       </c>
       <c r="K40" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="L40" s="5">
         <v>0.79166666666666663</v>
       </c>
-      <c r="L40" s="5">
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!B:B,"")</f>
@@ -2501,13 +2501,14 @@
       </c>
       <c r="E41">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!D:D,"")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F41" t="str">
         <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!C:C,"")</f>
-        <v>NL</v>
+        <v>KL</v>
       </c>
       <c r="G41">
+        <f>_xlfn.XLOOKUP(C41,EventTypes!A:A,EventTypes!E:E,"")</f>
         <v>0</v>
       </c>
       <c r="H41">
@@ -2515,10 +2516,10 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" s="4">
-        <v>46092</v>
+        <v>46087</v>
       </c>
       <c r="K41" s="5">
         <v>0.79166666666666663</v>
@@ -2527,12 +2528,12 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
@@ -2554,120 +2555,162 @@
       </c>
       <c r="H42">
         <f>_xlfn.XLOOKUP(C42,EventTypes!A:A,EventTypes!F:F,"")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4">
+        <v>46092</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!B:B,"")</f>
+        <v>Basic</v>
+      </c>
+      <c r="E43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!D:D,"")</f>
+        <v>80</v>
+      </c>
+      <c r="F43" t="str">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!C:C,"")</f>
+        <v>NL</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <f>_xlfn.XLOOKUP(C43,EventTypes!A:A,EventTypes!F:F,"")</f>
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43" s="4">
         <v>46112</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K43" s="5">
         <v>0.75</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L43" s="5">
         <v>0.875</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J43" s="4"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2679,7 +2722,7 @@
           <x14:formula1>
             <xm:f>EventTypes!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C62</xm:sqref>
+          <xm:sqref>C2:C63</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2690,14 +2733,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -2708,7 +2751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2719,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2730,7 +2773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2741,7 +2784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2752,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2763,7 +2806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2774,7 +2817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2785,7 +2828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2796,7 +2839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2807,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2818,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2829,7 +2872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2840,7 +2883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2851,7 +2894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2862,7 +2905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2873,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2884,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2895,7 +2938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2906,7 +2949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2917,7 +2960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2928,7 +2971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2939,7 +2982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2950,7 +2993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2961,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2972,7 +3015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2983,7 +3026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2994,7 +3037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3005,7 +3048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3016,7 +3059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3027,7 +3070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3038,7 +3081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3049,7 +3092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3060,7 +3103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3071,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3082,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3093,7 +3136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3104,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3115,7 +3158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3126,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3137,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3148,7 +3191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3167,21 +3210,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -3279,7 +3322,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3377,12 +3420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3396,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3410,12 +3453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3513,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3611,12 +3654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3648,22 +3691,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3674,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3682,12 +3725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3695,12 +3738,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3750,17 +3793,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3858,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3869,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3967,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3987,7 +4030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4085,12 +4128,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4098,7 +4141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4109,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4123,17 +4166,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4168,7 +4211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4182,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4226,17 +4269,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4247,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4255,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4263,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4286,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4298,14 +4341,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
-  <dimension ref="A1:AQ42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AQ43"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4479,7 +4522,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4489,7 +4532,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4499,7 +4542,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4509,7 +4552,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4519,7 +4562,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4529,7 +4572,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4539,7 +4582,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4549,7 +4592,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4559,7 +4602,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4569,7 +4612,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4579,7 +4622,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4589,7 +4632,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4599,7 +4642,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4609,7 +4652,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4619,7 +4662,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4629,7 +4672,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4639,7 +4682,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4649,7 +4692,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4659,7 +4702,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4669,7 +4712,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4679,7 +4722,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4689,7 +4732,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4699,7 +4742,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4709,183 +4752,193 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
       </c>
       <c r="B25" s="4">
         <f>Events!J25</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
       </c>
       <c r="B26" s="4">
         <f>Events!J26</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f>Events!B27</f>
-        <v>EÁ</v>
+        <v>HT</v>
       </c>
       <c r="B27" s="4">
         <f>Events!J27</f>
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
       </c>
       <c r="B28" s="4">
         <f>Events!J28</f>
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
       </c>
       <c r="B29" s="4">
         <f>Events!J29</f>
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f>Events!B30</f>
-        <v>Múlinn</v>
+        <v>EÁ</v>
       </c>
       <c r="B30" s="4">
         <f>Events!J30</f>
-        <v>46085</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
       </c>
       <c r="B31" s="4">
         <f>Events!J31</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
       </c>
       <c r="B32" s="4">
         <f>Events!J32</f>
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
       </c>
       <c r="B33" s="4">
         <f>Events!J33</f>
-        <v>46106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f>Events!B34</f>
-        <v>UR</v>
+        <v>Múlinn</v>
       </c>
       <c r="B34" s="4">
         <f>Events!J34</f>
-        <v>46091</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f>Events!B35</f>
-        <v>KD</v>
+        <v>UR</v>
       </c>
       <c r="B35" s="4">
         <f>Events!J35</f>
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f>Events!B36</f>
-        <v>JN</v>
+        <v>KD</v>
       </c>
       <c r="B36" s="4">
         <f>Events!J36</f>
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f>Events!B37</f>
-        <v>K&amp;B</v>
+        <v>JN</v>
       </c>
       <c r="B37" s="4">
         <f>Events!J37</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f>Events!B38</f>
-        <v>Svef</v>
+        <v>K&amp;B</v>
       </c>
       <c r="B38" s="4">
         <f>Events!J38</f>
-        <v>46107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f>Events!B39</f>
-        <v>Sígildir</v>
+        <v>Svef</v>
       </c>
       <c r="B39" s="4">
         <f>Events!J39</f>
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f>Events!B40</f>
-        <v>tón</v>
+        <v>Sígildir</v>
       </c>
       <c r="B40" s="4">
         <f>Events!J40</f>
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f>Events!B41</f>
-        <v>ÖL</v>
+        <v>tón</v>
       </c>
       <c r="B41" s="4">
         <f>Events!J41</f>
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f>Events!B42</f>
-        <v>RF</v>
+        <v>ÖL</v>
       </c>
       <c r="B42" s="4">
         <f>Events!J42</f>
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="str">
+        <f>Events!B43</f>
+        <v>RF</v>
+      </c>
+      <c r="B43" s="4">
+        <f>Events!J43</f>
         <v>46112</v>
       </c>
     </row>
@@ -4897,12 +4950,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4913,7 +4966,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -4924,7 +4977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -4935,7 +4988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4946,7 +4999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4957,7 +5010,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -4968,7 +5021,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -4980,7 +5033,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -4991,7 +5044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5002,7 +5055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5013,7 +5066,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -5024,7 +5077,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5035,7 +5088,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5046,7 +5099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5057,7 +5110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5068,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5079,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5090,7 +5143,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5101,7 +5154,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -5112,7 +5165,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -5123,7 +5176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -5134,7 +5187,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5145,7 +5198,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5156,7 +5209,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -5167,7 +5220,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -5178,7 +5231,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -5189,7 +5242,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -5201,7 +5254,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -5213,7 +5266,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -5225,7 +5278,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -5236,7 +5289,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5244,10 +5297,10 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -5258,7 +5311,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -5269,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -5280,7 +5333,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -5291,7 +5344,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -5310,14 +5363,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5328,7 +5381,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5336,10 +5389,10 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5347,10 +5400,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5361,7 +5414,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5372,7 +5425,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5383,7 +5436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5394,7 +5447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5405,7 +5458,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5416,7 +5469,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5435,17 +5488,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5468,7 +5521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5491,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5514,7 +5567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5537,7 +5590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5548,7 +5601,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5560,7 +5613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5583,7 +5636,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5606,7 +5659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5629,7 +5682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5652,7 +5705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5663,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5675,7 +5728,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5686,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="D11">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5698,7 +5751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5721,7 +5774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5732,7 +5785,7 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5744,7 +5797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5755,7 +5808,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5767,7 +5820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5781,16 +5834,16 @@
         <v>80</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reykjavikuniversity-my.sharepoint.com/personal/katrin23_ru_is/Documents/BSc Rekstrarverkfræði/3. ár/Verkfræði X/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8012448-62C7-440D-8B04-E5A2D25F4758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE762130-2A11-484C-BC19-5091CB9F833A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="111">
   <si>
     <t>Event</t>
   </si>
@@ -777,17 +777,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" customWidth="1"/>
-    <col min="9" max="11" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -910,7 +910,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -953,7 +953,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -995,7 +995,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2612,102 +2612,102 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
       <c r="J63" s="4"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
@@ -2733,14 +2733,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3210,21 +3210,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3420,12 +3420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3453,12 +3453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3654,12 +3654,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3691,22 +3691,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3725,12 +3725,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3738,12 +3738,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3793,17 +3793,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4128,12 +4128,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4166,17 +4166,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4269,17 +4269,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4342,13 +4342,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4522,7 +4522,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4532,7 +4532,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4542,7 +4542,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4552,7 +4552,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4562,7 +4562,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4572,7 +4572,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4582,7 +4582,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4592,7 +4592,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4602,7 +4602,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4612,7 +4612,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4622,7 +4622,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4632,7 +4632,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4642,7 +4642,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4652,7 +4652,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4662,7 +4662,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4672,7 +4672,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4682,7 +4682,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4692,7 +4692,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4702,7 +4702,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4712,7 +4712,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4722,7 +4722,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4732,7 +4732,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4742,7 +4742,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4752,7 +4752,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4762,7 +4762,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4772,7 +4772,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4782,7 +4782,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4792,7 +4792,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4802,7 +4802,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4812,7 +4812,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4822,7 +4822,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4832,7 +4832,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4842,7 +4842,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4852,7 +4852,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4862,7 +4862,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4872,7 +4872,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -4882,7 +4882,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -4892,7 +4892,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -4902,7 +4902,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
@@ -4912,7 +4912,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -4922,7 +4922,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -4932,7 +4932,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -4949,13 +4949,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5088,7 +5088,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5154,204 +5154,193 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>41</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>41</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>41</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>-80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>-160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>42</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <f>+C25*2</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>42</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <f>+C26*2</f>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>42</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <f>+C27*2</f>
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <f>+C28*2</f>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>47</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>47</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>47</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>-60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-      <c r="C36">
         <v>-100</v>
       </c>
     </row>
@@ -5363,14 +5352,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5381,7 +5370,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5392,7 +5381,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5403,7 +5392,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5414,7 +5403,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5425,7 +5414,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5436,7 +5425,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5447,7 +5436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5458,7 +5447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5469,7 +5458,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5488,17 +5477,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5521,7 +5510,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5544,7 +5533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5567,7 +5556,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5590,7 +5579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5613,7 +5602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5636,7 +5625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5659,7 +5648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5705,7 +5694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5728,7 +5717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5751,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5774,7 +5763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5797,7 +5786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5820,7 +5809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5843,7 +5832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>

--- a/Data/03_26.xlsx
+++ b/Data/03_26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silja\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE762130-2A11-484C-BC19-5091CB9F833A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3750A9A0-C947-4240-882C-9813BBD3DE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="22900" windowHeight="15240" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -777,17 +777,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E5C5EB-2E56-4141-9621-F1338A9E2497}">
   <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" customWidth="1"/>
-    <col min="9" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="9" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -868,7 +868,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -910,7 +910,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -953,7 +953,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -995,7 +995,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0.95833333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>0.89583333333333337</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2612,102 +2612,102 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J44" s="4"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J45" s="4"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J46" s="4"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J47" s="4"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="J48" s="4"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J49" s="4"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J51" s="4"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J52" s="4"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J53" s="4"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J54" s="4"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J55" s="4"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J56" s="4"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J57" s="4"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J58" s="4"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J59" s="4"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J60" s="4"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J61" s="4"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J62" s="4"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
-    <row r="63" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J63" s="4"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
@@ -2733,14 +2733,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3E7962-E1C3-4454-B671-E05683B75313}">
   <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3210,21 +3210,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B927A21B-584F-4957-BCD6-8FFB7A80A030}">
   <dimension ref="A1:AF42"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="14.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5" bestFit="1" customWidth="1"/>
     <col min="23" max="31" width="15" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3420,12 +3420,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3453,12 +3453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3654,12 +3654,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3691,22 +3757,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3717,7 +3783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3725,12 +3791,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3738,12 +3804,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3793,17 +3859,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3901,7 +3967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3912,7 +3978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4010,7 +4076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4030,7 +4096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4128,12 +4194,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4141,7 +4207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4152,7 +4218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4166,17 +4232,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4211,7 +4277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4225,7 +4291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4269,17 +4335,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4290,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4298,7 +4364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4306,7 +4372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4329,7 +4395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4342,13 +4408,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
   <dimension ref="A1:AQ43"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4522,7 +4588,7 @@
         <v xml:space="preserve">Þórey </v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4532,7 +4598,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4542,7 +4608,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4552,7 +4618,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4562,7 +4628,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4572,7 +4638,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4582,7 +4648,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4592,7 +4658,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4602,7 +4668,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4612,7 +4678,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4622,7 +4688,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4632,7 +4698,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4642,7 +4708,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4652,7 +4718,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4662,7 +4728,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
@@ -4672,7 +4738,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>Events!B17</f>
         <v>MT</v>
@@ -4682,7 +4748,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>Events!B18</f>
         <v>MT</v>
@@ -4692,7 +4758,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f>Events!B19</f>
         <v>MT</v>
@@ -4702,7 +4768,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f>Events!B20</f>
         <v>MT</v>
@@ -4712,7 +4778,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f>Events!B21</f>
         <v>MT</v>
@@ -4722,7 +4788,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f>Events!B22</f>
         <v>PF</v>
@@ -4732,7 +4798,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f>Events!B23</f>
         <v>RP</v>
@@ -4742,7 +4808,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f>Events!B24</f>
         <v>Fam</v>
@@ -4752,7 +4818,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f>Events!B25</f>
         <v>HT</v>
@@ -4762,7 +4828,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f>Events!B26</f>
         <v>HT</v>
@@ -4772,7 +4838,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f>Events!B27</f>
         <v>HT</v>
@@ -4782,7 +4848,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f>Events!B28</f>
         <v>EÁ</v>
@@ -4792,7 +4858,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f>Events!B29</f>
         <v>EÁ</v>
@@ -4802,7 +4868,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f>Events!B30</f>
         <v>EÁ</v>
@@ -4812,7 +4878,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f>Events!B31</f>
         <v>Múlinn</v>
@@ -4822,7 +4888,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f>Events!B32</f>
         <v>Múlinn</v>
@@ -4832,7 +4898,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f>Events!B33</f>
         <v>Múlinn</v>
@@ -4842,7 +4908,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f>Events!B34</f>
         <v>Múlinn</v>
@@ -4852,7 +4918,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f>Events!B35</f>
         <v>UR</v>
@@ -4862,7 +4928,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f>Events!B36</f>
         <v>KD</v>
@@ -4872,7 +4938,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f>Events!B37</f>
         <v>JN</v>
@@ -4882,7 +4948,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
         <f>Events!B38</f>
         <v>K&amp;B</v>
@@ -4892,7 +4958,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f>Events!B39</f>
         <v>Svef</v>
@@ -4902,7 +4968,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f>Events!B40</f>
         <v>Sígildir</v>
@@ -4912,7 +4978,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f>Events!B41</f>
         <v>tón</v>
@@ -4922,7 +4988,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
         <f>Events!B42</f>
         <v>ÖL</v>
@@ -4932,7 +4998,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
         <f>Events!B43</f>
         <v>RF</v>
@@ -4950,12 +5016,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCED54E1-26EA-4C6C-A87B-6FC746D3DCD2}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4966,7 +5032,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -4977,7 +5043,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -4988,7 +5054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -4999,7 +5065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -5010,7 +5076,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -5021,7 +5087,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -5033,7 +5099,7 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -5044,7 +5110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5066,7 +5132,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -5077,7 +5143,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5088,7 +5154,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -5099,7 +5165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -5110,7 +5176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -5121,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -5132,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -5143,7 +5209,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -5154,7 +5220,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -5165,7 +5231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -5176,7 +5242,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -5187,7 +5253,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -5198,7 +5264,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -5209,7 +5275,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -5220,7 +5286,7 @@
         <v>-160</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -5231,7 +5297,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -5243,7 +5309,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -5255,7 +5321,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -5267,7 +5333,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -5278,7 +5344,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -5289,7 +5355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -5300,7 +5366,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -5311,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -5322,7 +5388,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -5333,7 +5399,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -5352,14 +5418,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E6AA9DD-5344-4AFD-8E5D-E1460669ACF9}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5370,7 +5436,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5381,7 +5447,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5392,7 +5458,7 @@
         <v>-10000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5403,7 +5469,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5414,7 +5480,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5425,7 +5491,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -5436,7 +5502,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5447,7 +5513,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>3</v>
       </c>
@@ -5458,7 +5524,7 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5477,17 +5543,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60ED287-5985-48C0-88D9-B8B2B82FB872}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.81640625" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -5510,7 +5576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -5533,7 +5599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5556,7 +5622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5579,7 +5645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5602,7 +5668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5625,7 +5691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5648,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5671,7 +5737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5694,7 +5760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -5717,7 +5783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -5740,7 +5806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -5763,7 +5829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5786,7 +5852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -5809,7 +5875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -5832,7 +5898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
